--- a/resources/Dose_Response_Library.xlsx
+++ b/resources/Dose_Response_Library.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/anderson_timothy_epa_gov/Documents/Profile/Documents/Air Toxics Assessment Group/Dose-response library/HEM5 updates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_HEM4\HEM4\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{62BDCC04-B475-4CF0-B975-AC5C67831EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F4C0064-351B-4A63-A29A-E1A5080E7C2A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8EA491-702F-4ABF-A6CD-FFA881D04658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dose Response Value Library" sheetId="1" r:id="rId1"/>
@@ -82,10 +82,6 @@
 (mg/m3)</t>
   </si>
   <si>
-    <t>ERPG-2
-(mg/m3)</t>
-  </si>
-  <si>
     <t>1,1,1-Trichloroethane</t>
   </si>
   <si>
@@ -1957,14 +1953,18 @@
     </r>
   </si>
   <si>
-    <t>Acute REL
+    <t>1-Bromopropane</t>
+  </si>
+  <si>
+    <t>106-94-5</t>
+  </si>
+  <si>
+    <t>Acute NCREL
 (mg/m3)</t>
   </si>
   <si>
-    <t>1-Bromopropane</t>
-  </si>
-  <si>
-    <t>106-94-5</t>
+    <t>NCERPG-2
+(mg/m3)</t>
   </si>
 </sst>
 </file>
@@ -2461,7 +2461,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2537,10 +2537,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="47">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -2973,22 +2969,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J499"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.7265625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" customWidth="1"/>
+    <col min="1" max="1" width="36.77734375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" customWidth="1"/>
     <col min="3" max="3" width="14" style="26" customWidth="1"/>
     <col min="4" max="4" width="21" style="6" customWidth="1"/>
     <col min="5" max="5" width="11" style="6" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="27" customWidth="1"/>
-    <col min="7" max="7" width="9.26953125" style="27" customWidth="1"/>
-    <col min="8" max="8" width="9.7265625" style="27" customWidth="1"/>
-    <col min="9" max="9" width="9.26953125" style="27" customWidth="1"/>
+    <col min="6" max="6" width="8.77734375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" style="27" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" style="27" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" style="27" customWidth="1"/>
     <col min="10" max="10" width="12" style="27" customWidth="1"/>
-    <col min="11" max="16384" width="9.1796875" style="6"/>
+    <col min="11" max="16384" width="9.21875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3002,7 +2998,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -3014,18 +3010,18 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>7</v>
+        <v>630</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="5">
         <v>71556</v>
@@ -3054,10 +3050,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5">
         <v>79345</v>
@@ -3074,10 +3070,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="5">
         <v>79005</v>
@@ -3094,10 +3090,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5">
         <v>57147</v>
@@ -3118,10 +3114,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="C6" s="5">
         <v>319846</v>
@@ -3138,10 +3134,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="5">
         <v>319857</v>
@@ -3158,10 +3154,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5">
         <v>58899</v>
@@ -3178,10 +3174,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="5">
         <v>608731</v>
@@ -3200,10 +3196,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="5">
         <v>120821</v>
@@ -3222,10 +3218,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="C11" s="5">
         <v>96128</v>
@@ -3244,10 +3240,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="5">
         <v>122667</v>
@@ -3266,10 +3262,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="5">
         <v>106887</v>
@@ -3292,10 +3288,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="5">
         <v>75558</v>
@@ -3316,10 +3312,10 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5">
         <v>106990</v>
@@ -3346,10 +3342,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="5">
         <v>542756</v>
@@ -3368,10 +3364,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="5">
         <v>1120714</v>
@@ -3390,10 +3386,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="C18" s="5">
         <v>106467</v>
@@ -3412,10 +3408,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="C19" s="5">
         <v>60117</v>
@@ -3434,10 +3430,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="5">
         <v>123911</v>
@@ -3462,15 +3458,15 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>630</v>
-      </c>
-      <c r="D21" s="42">
+        <v>627</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="D21" s="4">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="E21" s="4"/>
@@ -3482,10 +3478,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22" s="8">
         <v>540841</v>
@@ -3500,10 +3496,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" s="5">
         <v>95954</v>
@@ -3522,10 +3518,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" s="5">
         <v>88062</v>
@@ -3544,10 +3540,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="C25" s="5">
         <v>94757</v>
@@ -3566,10 +3562,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="5">
         <v>51285</v>
@@ -3588,10 +3584,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>25321146</v>
@@ -3608,10 +3604,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="5">
         <v>121142</v>
@@ -3628,10 +3624,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29" s="5">
         <v>95807</v>
@@ -3650,10 +3646,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="C30" s="5">
         <v>26471625</v>
@@ -3682,10 +3678,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" s="5">
         <v>584849</v>
@@ -3714,10 +3710,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="5">
         <v>532274</v>
@@ -3734,10 +3730,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" s="5">
         <v>79469</v>
@@ -3756,10 +3752,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" s="5">
         <v>91941</v>
@@ -3778,10 +3774,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" s="5">
         <v>119904</v>
@@ -3798,10 +3794,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" s="5">
         <v>119937</v>
@@ -3818,10 +3814,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="5">
         <v>101144</v>
@@ -3840,10 +3836,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C38" s="5">
         <v>101779</v>
@@ -3862,10 +3858,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="C39" s="5">
         <v>101688</v>
@@ -3888,10 +3884,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="C40" s="5">
         <v>534521</v>
@@ -3910,10 +3906,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C41" s="8">
         <v>92671</v>
@@ -3928,10 +3924,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C42" s="8">
         <v>92933</v>
@@ -3946,10 +3942,10 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" s="5">
         <v>100027</v>
@@ -3968,10 +3964,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C44" s="5">
         <v>75070</v>
@@ -4000,10 +3996,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" s="5">
         <v>60355</v>
@@ -4022,10 +4018,10 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" s="5">
         <v>75058</v>
@@ -4048,10 +4044,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C47" s="5">
         <v>98862</v>
@@ -4070,10 +4066,10 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C48" s="10">
         <v>107028</v>
@@ -4102,10 +4098,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C49" s="5">
         <v>79061</v>
@@ -4124,10 +4120,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" s="5">
         <v>79107</v>
@@ -4156,10 +4152,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" s="5">
         <v>107131</v>
@@ -4184,10 +4180,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" s="5">
         <v>107051</v>
@@ -4214,10 +4210,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C53" s="5">
         <v>62533</v>
@@ -4240,10 +4236,10 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C54" s="5">
         <v>90040</v>
@@ -4262,10 +4258,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" s="5">
         <v>7440360</v>
@@ -4284,10 +4280,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" s="5">
         <v>1327339</v>
@@ -4304,13 +4300,13 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4">
@@ -4324,10 +4320,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58" s="5">
         <v>1314609</v>
@@ -4346,10 +4342,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" s="5">
         <v>304610</v>
@@ -4368,10 +4364,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C60" s="5">
         <v>1332816</v>
@@ -4390,13 +4386,13 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4">
@@ -4414,10 +4410,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C62" s="5">
         <v>1309644</v>
@@ -4436,10 +4432,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="C63" s="5">
         <v>7778394</v>
@@ -4460,10 +4456,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C64" s="8">
         <v>7784409</v>
@@ -4484,13 +4480,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>81</v>
       </c>
       <c r="D65" s="4">
         <v>4.3E-3</v>
@@ -4508,13 +4504,13 @@
     </row>
     <row r="66" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C66" s="14" t="s">
         <v>82</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>83</v>
       </c>
       <c r="D66" s="15">
         <v>4.3E-3</v>
@@ -4534,13 +4530,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="D67" s="4">
         <v>4.3E-3</v>
@@ -4558,10 +4554,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C68" s="5">
         <v>1327533</v>
@@ -4584,10 +4580,10 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C69" s="5">
         <v>7784421</v>
@@ -4610,10 +4606,10 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C70" s="5">
         <v>71432</v>
@@ -4640,10 +4636,10 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C71" s="5">
         <v>92875</v>
@@ -4660,10 +4656,10 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C72" s="5">
         <v>98077</v>
@@ -4680,10 +4676,10 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C73" s="5">
         <v>100447</v>
@@ -4708,13 +4704,13 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="D74" s="4">
         <v>2.3999999999999998E-3</v>
@@ -4730,10 +4726,10 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C75" s="5">
         <v>7440417</v>
@@ -4754,13 +4750,13 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="D76" s="4">
         <v>2.3999999999999998E-3</v>
@@ -4776,13 +4772,13 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="D77" s="4">
         <v>2.3999999999999998E-3</v>
@@ -4798,13 +4794,13 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="D78" s="4">
         <v>2.3999999999999998E-3</v>
@@ -4820,10 +4816,10 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C79" s="5">
         <v>57578</v>
@@ -4838,10 +4834,10 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C80" s="5">
         <v>92524</v>
@@ -4862,10 +4858,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C81" s="5">
         <v>117817</v>
@@ -4882,10 +4878,10 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C82" s="5">
         <v>542881</v>
@@ -4908,10 +4904,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C83" s="5">
         <v>75252</v>
@@ -4930,10 +4926,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="C84" s="8">
         <v>543908</v>
@@ -4952,10 +4948,10 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C85" s="5">
         <v>7440439</v>
@@ -4978,13 +4974,13 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="D86" s="4">
         <v>1.8E-3</v>
@@ -5000,10 +4996,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C87" s="5">
         <v>10325947</v>
@@ -5022,10 +5018,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C88" s="8">
         <v>1306190</v>
@@ -5044,13 +5040,13 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C89" s="12" t="s">
         <v>112</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C89" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="D89" s="4">
         <v>1.8E-3</v>
@@ -5066,10 +5062,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C90" s="5">
         <v>133062</v>
@@ -5086,10 +5082,10 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C91" s="5">
         <v>63252</v>
@@ -5108,10 +5104,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C92" s="5">
         <v>75150</v>
@@ -5140,10 +5136,10 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C93" s="5">
         <v>56235</v>
@@ -5170,10 +5166,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B94" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="C94" s="8">
         <v>463581</v>
@@ -5192,10 +5188,10 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C95" s="8">
         <v>120809</v>
@@ -5210,10 +5206,10 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C96" s="5">
         <v>133904</v>
@@ -5232,10 +5228,10 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C97" s="5">
         <v>57749</v>
@@ -5254,10 +5250,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C98" s="5">
         <v>7782505</v>
@@ -5286,10 +5282,10 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C99" s="5">
         <v>79118</v>
@@ -5310,10 +5306,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C100" s="5">
         <v>108907</v>
@@ -5336,10 +5332,10 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C101" s="5">
         <v>510156</v>
@@ -5358,10 +5354,10 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C102" s="5">
         <v>67663</v>
@@ -5386,10 +5382,10 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C103" s="5">
         <v>107302</v>
@@ -5412,10 +5408,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C104" s="5">
         <v>126998</v>
@@ -5434,10 +5430,10 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="C105" s="8">
         <v>7788989</v>
@@ -5456,10 +5452,10 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C106" s="8">
         <v>7789095</v>
@@ -5478,10 +5474,10 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C107" s="8">
         <v>10294403</v>
@@ -5500,10 +5496,10 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C108" s="28">
         <v>13765190</v>
@@ -5522,13 +5518,13 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C109" s="30" t="s">
         <v>135</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C109" s="30" t="s">
-        <v>136</v>
       </c>
       <c r="D109" s="4">
         <v>1.839E-2</v>
@@ -5544,10 +5540,10 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C110" s="5">
         <v>1308389</v>
@@ -5562,10 +5558,10 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C111" s="5">
         <v>10101538</v>
@@ -5580,10 +5576,10 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C112" s="5">
         <v>13530682</v>
@@ -5602,10 +5598,10 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C113" s="5">
         <v>16065831</v>
@@ -5624,10 +5620,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C114" s="8">
         <v>7758976</v>
@@ -5646,10 +5642,10 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C115" s="28">
         <v>18454121</v>
@@ -5668,10 +5664,10 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C116" s="5">
         <v>18540299</v>
@@ -5690,10 +5686,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C117" s="5">
         <v>11115745</v>
@@ -5712,13 +5708,13 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -5730,10 +5726,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C119" s="5">
         <v>7440473</v>
@@ -5752,10 +5748,10 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C120" s="5">
         <v>12018018</v>
@@ -5774,10 +5770,10 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C121" s="5">
         <v>12018198</v>
@@ -5792,10 +5788,10 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C122" s="5">
         <v>7789006</v>
@@ -5814,10 +5810,10 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C123" s="5">
         <v>7778509</v>
@@ -5836,10 +5832,10 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C124" s="8">
         <v>7775113</v>
@@ -5858,10 +5854,10 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C125" s="8">
         <v>10588019</v>
@@ -5880,10 +5876,10 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C126" s="8">
         <v>7789062</v>
@@ -5902,10 +5898,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C127" s="28">
         <v>13530659</v>
@@ -5924,10 +5920,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C128" s="28">
         <v>50922297</v>
@@ -5942,10 +5938,10 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C129" s="8">
         <v>11103869</v>
@@ -5964,10 +5960,10 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B130" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="C130" s="5">
         <v>1345160</v>
@@ -5984,13 +5980,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C131" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="4">
@@ -6004,13 +6000,13 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C132" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4">
@@ -6024,13 +6020,13 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C133" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4">
@@ -6044,13 +6040,13 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C134" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4">
@@ -6064,10 +6060,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C135" s="5">
         <v>7440484</v>
@@ -6086,13 +6082,13 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C136" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4">
@@ -6108,10 +6104,10 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C137" s="5">
         <v>61789513</v>
@@ -6128,13 +6124,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C138" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4">
@@ -6148,10 +6144,10 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C139" s="5">
         <v>1307966</v>
@@ -6168,10 +6164,10 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C140" s="5">
         <v>1308061</v>
@@ -6188,10 +6184,10 @@
     </row>
     <row r="141" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C141" s="5">
         <v>136527</v>
@@ -6208,10 +6204,10 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B142" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="C142" s="14">
         <v>141</v>
@@ -6228,10 +6224,10 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C143" s="5">
         <v>8007452</v>
@@ -6248,10 +6244,10 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C144" s="5">
         <v>8007452</v>
@@ -6270,10 +6266,10 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C145" s="14">
         <v>142</v>
@@ -6290,10 +6286,10 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B146" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="C146" s="5">
         <v>1319773</v>
@@ -6312,10 +6308,10 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C147" s="5">
         <v>108394</v>
@@ -6334,10 +6330,10 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C148" s="5">
         <v>95487</v>
@@ -6356,10 +6352,10 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C149" s="5">
         <v>106445</v>
@@ -6378,10 +6374,10 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C150" s="5">
         <v>98828</v>
@@ -6404,10 +6400,10 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B151" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="C151" s="5">
         <v>75865</v>
@@ -6430,13 +6426,13 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C152" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C152" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4">
@@ -6450,13 +6446,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C153" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4">
@@ -6470,10 +6466,10 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C154" s="5">
         <v>592018</v>
@@ -6496,10 +6492,10 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C155" s="5">
         <v>544923</v>
@@ -6518,10 +6514,10 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C156" s="5">
         <v>21725462</v>
@@ -6538,13 +6534,13 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4">
@@ -6558,10 +6554,10 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C158" s="5">
         <v>57125</v>
@@ -6580,10 +6576,10 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C159" s="5">
         <v>460195</v>
@@ -6606,10 +6602,10 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C160" s="5">
         <v>506683</v>
@@ -6628,10 +6624,10 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C161" s="5">
         <v>506774</v>
@@ -6652,13 +6648,13 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C162" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4">
@@ -6672,13 +6668,13 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C163" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4">
@@ -6692,13 +6688,13 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C164" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4">
@@ -6712,10 +6708,10 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C165" s="5">
         <v>109784</v>
@@ -6734,10 +6730,10 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C166" s="5">
         <v>74908</v>
@@ -6764,10 +6760,10 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C167" s="8">
         <v>78820</v>
@@ -6790,10 +6786,10 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C168" s="5">
         <v>151508</v>
@@ -6816,10 +6812,10 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C169" s="5">
         <v>506616</v>
@@ -6838,13 +6834,13 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C170" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4">
@@ -6858,10 +6854,10 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C171" s="5">
         <v>506649</v>
@@ -6880,10 +6876,10 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C172" s="5">
         <v>143339</v>
@@ -6906,13 +6902,13 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C173" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="D173" s="4">
         <v>0</v>
@@ -6928,10 +6924,10 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C174" s="5">
         <v>21564170</v>
@@ -6950,10 +6946,10 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C175" s="5">
         <v>557211</v>
@@ -6972,10 +6968,10 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B176" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="C176" s="5">
         <v>72559</v>
@@ -6992,13 +6988,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C177" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -7010,10 +7006,10 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C178" s="5">
         <v>132649</v>
@@ -7032,10 +7028,10 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C179" s="5">
         <v>84742</v>
@@ -7054,10 +7050,10 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C180" s="5">
         <v>111444</v>
@@ -7076,10 +7072,10 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C181" s="5">
         <v>62737</v>
@@ -7100,13 +7096,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C182" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="D182" s="4">
         <v>0</v>
@@ -7122,10 +7118,10 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C183" s="5">
         <v>111422</v>
@@ -7144,10 +7140,10 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B184" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="C184" s="8">
         <v>64675</v>
@@ -7162,10 +7158,10 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C185" s="5">
         <v>68122</v>
@@ -7190,10 +7186,10 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C186" s="5">
         <v>131113</v>
@@ -7212,10 +7208,10 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C187" s="5">
         <v>77781</v>
@@ -7238,10 +7234,10 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B188" s="7" t="s">
         <v>233</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>234</v>
       </c>
       <c r="C188" s="8">
         <v>79447</v>
@@ -7256,10 +7252,10 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C189" s="5">
         <v>3268879</v>
@@ -7278,10 +7274,10 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C190" s="5">
         <v>39001020</v>
@@ -7300,10 +7296,10 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C191" s="5">
         <v>35822469</v>
@@ -7322,10 +7318,10 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C192" s="5">
         <v>67562394</v>
@@ -7344,10 +7340,10 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C193" s="5">
         <v>55673897</v>
@@ -7366,10 +7362,10 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C194" s="5">
         <v>39227286</v>
@@ -7388,10 +7384,10 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C195" s="5">
         <v>70648269</v>
@@ -7410,10 +7406,10 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C196" s="5">
         <v>57653857</v>
@@ -7432,10 +7428,10 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C197" s="5">
         <v>57117449</v>
@@ -7454,10 +7450,10 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C198" s="5">
         <v>19408743</v>
@@ -7476,10 +7472,10 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C199" s="5">
         <v>72918219</v>
@@ -7498,10 +7494,10 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C200" s="5">
         <v>40321764</v>
@@ -7520,10 +7516,10 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C201" s="5">
         <v>57117416</v>
@@ -7542,10 +7538,10 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C202" s="5">
         <v>60851345</v>
@@ -7564,10 +7560,10 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C203" s="5">
         <v>57117314</v>
@@ -7586,10 +7582,10 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C204" s="5">
         <v>1746016</v>
@@ -7608,10 +7604,10 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C205" s="5">
         <v>51207319</v>
@@ -7630,10 +7626,10 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B206" s="32" t="s">
         <v>250</v>
-      </c>
-      <c r="B206" s="32" t="s">
-        <v>251</v>
       </c>
       <c r="C206" s="5">
         <v>34465468</v>
@@ -7652,10 +7648,10 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B207" s="32" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C207" s="5">
         <v>136677106</v>
@@ -7670,10 +7666,10 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C208" s="5">
         <v>106898</v>
@@ -7702,10 +7698,10 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C209" s="5">
         <v>140885</v>
@@ -7730,10 +7726,10 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C210" s="5">
         <v>100414</v>
@@ -7756,10 +7752,10 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C211" s="5">
         <v>51796</v>
@@ -7778,10 +7774,10 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C212" s="5">
         <v>75003</v>
@@ -7800,10 +7796,10 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C213" s="5">
         <v>106934</v>
@@ -7826,10 +7822,10 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C214" s="5">
         <v>107062</v>
@@ -7852,10 +7848,10 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C215" s="5">
         <v>107211</v>
@@ -7874,10 +7870,10 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C216" s="5">
         <v>151564</v>
@@ -7896,12 +7892,12 @@
       <c r="I216" s="4"/>
       <c r="J216" s="4"/>
     </row>
-    <row r="217" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C217" s="5">
         <v>75218</v>
@@ -7924,10 +7920,10 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C218" s="5">
         <v>96457</v>
@@ -7944,10 +7940,10 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C219" s="5">
         <v>75343</v>
@@ -7966,10 +7962,10 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C220" s="5">
         <v>50000</v>
@@ -7998,10 +7994,10 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C221" s="8">
         <v>110714</v>
@@ -8022,10 +8018,10 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C222" s="8">
         <v>112072</v>
@@ -8046,10 +8042,10 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C223" s="8">
         <v>112254</v>
@@ -8070,10 +8066,10 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C224" s="8">
         <v>20706256</v>
@@ -8092,10 +8088,10 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C225" s="8">
         <v>124174</v>
@@ -8116,10 +8112,10 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C226" s="5">
         <v>112152</v>
@@ -8138,10 +8134,10 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C227" s="8">
         <v>112367</v>
@@ -8160,10 +8156,10 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C228" s="8">
         <v>111966</v>
@@ -8184,10 +8180,10 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C229" s="8">
         <v>1002671</v>
@@ -8206,10 +8202,10 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C230" s="5">
         <v>112345</v>
@@ -8230,10 +8226,10 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C231" s="5">
         <v>111900</v>
@@ -8254,10 +8250,10 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C232" s="8">
         <v>111773</v>
@@ -8278,13 +8274,13 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C233" s="19" t="s">
         <v>285</v>
-      </c>
-      <c r="B233" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C233" s="19" t="s">
-        <v>286</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="4">
@@ -8300,10 +8296,10 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C234" s="5">
         <v>629141</v>
@@ -8322,10 +8318,10 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C235" s="5">
         <v>110805</v>
@@ -8346,10 +8342,10 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C236" s="5">
         <v>111159</v>
@@ -8370,10 +8366,10 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C237" s="5">
         <v>109864</v>
@@ -8394,10 +8390,10 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C238" s="5">
         <v>110496</v>
@@ -8418,10 +8414,10 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C239" s="5">
         <v>7795917</v>
@@ -8440,10 +8436,10 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C240" s="18">
         <v>171</v>
@@ -8464,10 +8460,10 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C241" s="8">
         <v>112356</v>
@@ -8488,13 +8484,13 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C242" s="12" t="s">
         <v>297</v>
-      </c>
-      <c r="B242" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C242" s="12" t="s">
-        <v>298</v>
       </c>
       <c r="D242" s="4"/>
       <c r="E242" s="4">
@@ -8510,10 +8506,10 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C243" s="8">
         <v>112594</v>
@@ -8534,10 +8530,10 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C244" s="8">
         <v>122996</v>
@@ -8558,10 +8554,10 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C245" s="8">
         <v>2807309</v>
@@ -8582,10 +8578,10 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C246" s="8">
         <v>112492</v>
@@ -8604,13 +8600,13 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C247" s="12" t="s">
         <v>617</v>
-      </c>
-      <c r="B247" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C247" s="12" t="s">
-        <v>618</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="4">
@@ -8626,10 +8622,10 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C248" s="5">
         <v>143226</v>
@@ -8648,10 +8644,10 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C249" s="5">
         <v>76448</v>
@@ -8670,10 +8666,10 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C250" s="5">
         <v>118741</v>
@@ -8690,10 +8686,10 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C251" s="5">
         <v>87683</v>
@@ -8714,10 +8710,10 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C252" s="5">
         <v>77474</v>
@@ -8736,10 +8732,10 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C253" s="5">
         <v>67721</v>
@@ -8756,10 +8752,10 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C254" s="5">
         <v>822060</v>
@@ -8778,10 +8774,10 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C255" s="5">
         <v>680319</v>
@@ -8796,10 +8792,10 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B256" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="B256" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="C256" s="5">
         <v>110543</v>
@@ -8820,10 +8816,10 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C257" s="5">
         <v>302012</v>
@@ -8850,10 +8846,10 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C258" s="5">
         <v>7647010</v>
@@ -8882,10 +8878,10 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C259" s="5">
         <v>7664393</v>
@@ -8914,10 +8910,10 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C260" s="5">
         <v>123319</v>
@@ -8936,10 +8932,10 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C261" s="5">
         <v>78591</v>
@@ -8956,10 +8952,10 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B262" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="B262" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="C262" s="8">
         <v>1317368</v>
@@ -8976,10 +8972,10 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C263" s="8">
         <v>301042</v>
@@ -8996,10 +8992,10 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C264" s="8">
         <v>7784409</v>
@@ -9018,10 +9014,10 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C265" s="8">
         <v>7758976</v>
@@ -9040,10 +9036,10 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C266" s="28">
         <v>18454121</v>
@@ -9062,13 +9058,13 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C267" s="30" t="s">
         <v>324</v>
-      </c>
-      <c r="B267" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="C267" s="30" t="s">
-        <v>325</v>
       </c>
       <c r="D267" s="4"/>
       <c r="E267" s="4">
@@ -9082,10 +9078,10 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C268" s="5">
         <v>7439921</v>
@@ -9104,10 +9100,10 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C269" s="14">
         <v>603</v>
@@ -9124,10 +9120,10 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C270" s="8">
         <v>1309600</v>
@@ -9146,10 +9142,10 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C271" s="8">
         <v>10099748</v>
@@ -9166,10 +9162,10 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C272" s="8">
         <v>1335326</v>
@@ -9186,10 +9182,10 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C273" s="8">
         <v>7446142</v>
@@ -9206,10 +9202,10 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C274" s="5">
         <v>78002</v>
@@ -9228,10 +9224,10 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C275" s="5">
         <v>75741</v>
@@ -9250,10 +9246,10 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C276" s="5">
         <v>108316</v>
@@ -9276,10 +9272,10 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B277" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="B277" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="C277" s="5">
         <v>2145076</v>
@@ -9296,10 +9292,10 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C278" s="5">
         <v>7439965</v>
@@ -9318,10 +9314,10 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C279" s="8">
         <v>1313139</v>
@@ -9340,10 +9336,10 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C280" s="8">
         <v>10377669</v>
@@ -9360,13 +9356,13 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C281" s="12" t="s">
         <v>338</v>
-      </c>
-      <c r="B281" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="C281" s="12" t="s">
-        <v>339</v>
       </c>
       <c r="D281" s="4"/>
       <c r="E281" s="4">
@@ -9380,10 +9376,10 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C282" s="8">
         <v>7785877</v>
@@ -9402,10 +9398,10 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C283" s="8">
         <v>1317357</v>
@@ -9420,12 +9416,12 @@
       <c r="I283" s="4"/>
       <c r="J283" s="4"/>
     </row>
-    <row r="284" spans="1:10" ht="25" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A284" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C284" s="8">
         <v>12079651</v>
@@ -9442,10 +9438,10 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C285" s="8">
         <v>1317346</v>
@@ -9464,10 +9460,10 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B286" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="B286" s="4" t="s">
-        <v>345</v>
       </c>
       <c r="C286" s="14">
         <v>201</v>
@@ -9484,13 +9480,13 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C287" s="5" t="s">
         <v>346</v>
-      </c>
-      <c r="B287" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C287" s="5" t="s">
-        <v>347</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4">
@@ -9504,10 +9500,10 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C288" s="5">
         <v>7487947</v>
@@ -9526,13 +9522,13 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C289" s="5" t="s">
         <v>349</v>
-      </c>
-      <c r="B289" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C289" s="5" t="s">
-        <v>350</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="4">
@@ -9546,13 +9542,13 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C290" s="5" t="s">
         <v>351</v>
-      </c>
-      <c r="B290" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C290" s="5" t="s">
-        <v>352</v>
       </c>
       <c r="D290" s="4"/>
       <c r="E290" s="4">
@@ -9566,10 +9562,10 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C291" s="5">
         <v>7439976</v>
@@ -9594,10 +9590,10 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C292" s="5">
         <v>22967926</v>
@@ -9614,13 +9610,13 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D293" s="4">
         <v>0</v>
@@ -9636,13 +9632,13 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C294" s="5" t="s">
         <v>356</v>
-      </c>
-      <c r="B294" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C294" s="5" t="s">
-        <v>357</v>
       </c>
       <c r="D294" s="4"/>
       <c r="E294" s="4">
@@ -9656,10 +9652,10 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C295" s="5">
         <v>22967926</v>
@@ -9678,13 +9674,13 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C296" s="5" t="s">
         <v>359</v>
-      </c>
-      <c r="B296" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C296" s="5" t="s">
-        <v>360</v>
       </c>
       <c r="D296" s="4"/>
       <c r="E296" s="4">
@@ -9698,10 +9694,10 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C297" s="14">
         <v>202</v>
@@ -9718,10 +9714,10 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C298" s="5">
         <v>62384</v>
@@ -9740,10 +9736,10 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C299" s="5">
         <v>67561</v>
@@ -9772,10 +9768,10 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C300" s="5">
         <v>72435</v>
@@ -9792,10 +9788,10 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C301" s="5">
         <v>74839</v>
@@ -9820,10 +9816,10 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C302" s="5">
         <v>74873</v>
@@ -9848,10 +9844,10 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C303" s="5">
         <v>60344</v>
@@ -9872,10 +9868,10 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C304" s="5">
         <v>74884</v>
@@ -9902,10 +9898,10 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C305" s="5">
         <v>108101</v>
@@ -9924,10 +9920,10 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C306" s="5">
         <v>624839</v>
@@ -9952,10 +9948,10 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C307" s="5">
         <v>80626</v>
@@ -9978,10 +9974,10 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C308" s="5">
         <v>1634044</v>
@@ -10006,12 +10002,12 @@
       </c>
       <c r="J308" s="4"/>
     </row>
-    <row r="309" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C309" s="5">
         <v>75092</v>
@@ -10040,10 +10036,10 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C310" s="5">
         <v>121697</v>
@@ -10062,10 +10058,10 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C311" s="5">
         <v>91203</v>
@@ -10084,10 +10080,10 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B312" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="B312" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="C312" s="8">
         <v>10101970</v>
@@ -10106,10 +10102,10 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C313" s="8">
         <v>373024</v>
@@ -10128,10 +10124,10 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C314" s="5">
         <v>13463393</v>
@@ -10152,10 +10148,10 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C315" s="5">
         <v>7718549</v>
@@ -10174,10 +10170,10 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C316" s="5">
         <v>7440020</v>
@@ -10196,10 +10192,10 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C317" s="5">
         <v>13138459</v>
@@ -10218,10 +10214,10 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C318" s="5">
         <v>1313991</v>
@@ -10240,13 +10236,13 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C319" s="5" t="s">
         <v>383</v>
-      </c>
-      <c r="B319" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C319" s="5" t="s">
-        <v>384</v>
       </c>
       <c r="D319" s="4">
         <v>2.4000000000000001E-4</v>
@@ -10260,10 +10256,10 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C320" s="5">
         <v>12035722</v>
@@ -10282,10 +10278,10 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C321" s="5">
         <v>13770893</v>
@@ -10304,10 +10300,10 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C322" s="5">
         <v>7786814</v>
@@ -10326,10 +10322,10 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C323" s="5">
         <v>98953</v>
@@ -10348,10 +10344,10 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C324" s="5">
         <v>62759</v>
@@ -10370,10 +10366,10 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C325" s="5">
         <v>59892</v>
@@ -10392,13 +10388,13 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B326" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="B326" s="4" t="s">
+      <c r="C326" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="C326" s="5" t="s">
-        <v>393</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
@@ -10410,10 +10406,10 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C327" s="5">
         <v>95534</v>
@@ -10432,10 +10428,10 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C328" s="5">
         <v>56382</v>
@@ -10456,10 +10452,10 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C329" s="5">
         <v>82688</v>
@@ -10476,10 +10472,10 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C330" s="5">
         <v>87865</v>
@@ -10496,10 +10492,10 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C331" s="5">
         <v>108952</v>
@@ -10528,10 +10524,10 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C332" s="5">
         <v>75445</v>
@@ -10556,10 +10552,10 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C333" s="5">
         <v>7803512</v>
@@ -10582,10 +10578,10 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C334" s="5">
         <v>7723140</v>
@@ -10606,10 +10602,10 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C335" s="5">
         <v>85449</v>
@@ -10628,13 +10624,13 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C336" s="5" t="s">
         <v>403</v>
-      </c>
-      <c r="B336" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="C336" s="5" t="s">
-        <v>404</v>
       </c>
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
@@ -10646,10 +10642,10 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B337" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="B337" s="4" t="s">
-        <v>406</v>
       </c>
       <c r="C337" s="5">
         <v>12674112</v>
@@ -10668,13 +10664,13 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C338" s="5" t="s">
         <v>407</v>
-      </c>
-      <c r="B338" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C338" s="5" t="s">
-        <v>408</v>
       </c>
       <c r="D338" s="4">
         <v>1E-4</v>
@@ -10688,13 +10684,13 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C339" s="5" t="s">
         <v>409</v>
-      </c>
-      <c r="B339" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C339" s="5" t="s">
-        <v>410</v>
       </c>
       <c r="D339" s="4">
         <v>1E-4</v>
@@ -10708,13 +10704,13 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C340" s="5" t="s">
         <v>411</v>
-      </c>
-      <c r="B340" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C340" s="5" t="s">
-        <v>412</v>
       </c>
       <c r="D340" s="4">
         <v>1E-4</v>
@@ -10728,10 +10724,10 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C341" s="5">
         <v>11097691</v>
@@ -10750,13 +10746,13 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C342" s="5" t="s">
         <v>414</v>
-      </c>
-      <c r="B342" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C342" s="5" t="s">
-        <v>415</v>
       </c>
       <c r="D342" s="4">
         <v>1E-4</v>
@@ -10770,10 +10766,10 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C343" s="5">
         <v>1336363</v>
@@ -10792,13 +10788,13 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C344" s="5" t="s">
         <v>624</v>
-      </c>
-      <c r="B344" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C344" s="5" t="s">
-        <v>625</v>
       </c>
       <c r="D344" s="4">
         <v>1E-4</v>
@@ -10812,10 +10808,10 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C345" s="5">
         <v>7012375</v>
@@ -10832,10 +10828,10 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C346" s="5">
         <v>2050682</v>
@@ -10852,10 +10848,10 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C347" s="5">
         <v>2051243</v>
@@ -10872,10 +10868,10 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C348" s="5">
         <v>28655712</v>
@@ -10892,10 +10888,10 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C349" s="5">
         <v>26601649</v>
@@ -10912,10 +10908,10 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C350" s="20">
         <v>25429292</v>
@@ -10932,10 +10928,10 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C351" s="5">
         <v>26914330</v>
@@ -10952,10 +10948,10 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B352" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="B352" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="C352" s="5"/>
       <c r="D352" s="31">
@@ -10970,10 +10966,10 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B353" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="B353" s="4" t="s">
-        <v>427</v>
       </c>
       <c r="C353" s="38">
         <v>40</v>
@@ -10990,13 +10986,13 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B354" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B354" s="4" t="s">
-        <v>429</v>
-      </c>
       <c r="C354" s="38" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D354" s="31">
         <v>5.079E-5</v>
@@ -11010,10 +11006,10 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C355" s="38">
         <v>246</v>
@@ -11030,10 +11026,10 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B356" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="B356" s="4" t="s">
-        <v>432</v>
       </c>
       <c r="C356" s="5"/>
       <c r="D356" s="31">
@@ -11048,10 +11044,10 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B357" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="B357" s="4" t="s">
-        <v>434</v>
       </c>
       <c r="C357" s="5">
         <v>90120</v>
@@ -11070,10 +11066,10 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C358" s="5">
         <v>832699</v>
@@ -11090,13 +11086,13 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C359" s="39" t="s">
         <v>621</v>
-      </c>
-      <c r="B359" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C359" s="39" t="s">
-        <v>622</v>
       </c>
       <c r="D359" s="31">
         <v>5.079E-5</v>
@@ -11110,10 +11106,10 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C360" s="5">
         <v>2381217</v>
@@ -11130,10 +11126,10 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C361" s="5">
         <v>91576</v>
@@ -11152,13 +11148,13 @@
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C362" s="12" t="s">
         <v>438</v>
-      </c>
-      <c r="B362" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C362" s="12" t="s">
-        <v>439</v>
       </c>
       <c r="D362" s="31">
         <v>5.079E-5</v>
@@ -11172,10 +11168,10 @@
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C363" s="12">
         <v>2422799</v>
@@ -11192,10 +11188,10 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C364" s="5">
         <v>91587</v>
@@ -11214,10 +11210,10 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B365" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="B365" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="C365" s="5">
         <v>83329</v>
@@ -11236,10 +11232,10 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C366" s="5">
         <v>208968</v>
@@ -11258,10 +11254,10 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B367" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="B367" s="4" t="s">
-        <v>446</v>
       </c>
       <c r="C367" s="5">
         <v>120127</v>
@@ -11278,10 +11274,10 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C368" s="5">
         <v>203338</v>
@@ -11298,13 +11294,13 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C369" s="38" t="s">
         <v>504</v>
-      </c>
-      <c r="B369" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C369" s="38" t="s">
-        <v>505</v>
       </c>
       <c r="D369" s="31">
         <v>5.079E-5</v>
@@ -11318,10 +11314,10 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C370" s="8">
         <v>195197</v>
@@ -11338,10 +11334,10 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C371" s="5">
         <v>192972</v>
@@ -11360,10 +11356,10 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C372" s="5">
         <v>56832736</v>
@@ -11380,10 +11376,10 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C373" s="5">
         <v>191242</v>
@@ -11402,13 +11398,13 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C374" s="5" t="s">
         <v>453</v>
-      </c>
-      <c r="B374" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="C374" s="5" t="s">
-        <v>454</v>
       </c>
       <c r="D374" s="31">
         <v>5.079E-5</v>
@@ -11422,10 +11418,10 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C375" s="38">
         <v>284</v>
@@ -11442,10 +11438,10 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C376" s="5">
         <v>206440</v>
@@ -11464,10 +11460,10 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C377" s="5">
         <v>86737</v>
@@ -11486,13 +11482,13 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C378" s="5" t="s">
         <v>458</v>
-      </c>
-      <c r="B378" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C378" s="5" t="s">
-        <v>459</v>
       </c>
       <c r="D378" s="31">
         <v>5.079E-5</v>
@@ -11506,10 +11502,10 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C379" s="5">
         <v>26914181</v>
@@ -11526,13 +11522,13 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C380" s="5" t="s">
         <v>611</v>
-      </c>
-      <c r="B380" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C380" s="5" t="s">
-        <v>612</v>
       </c>
       <c r="D380" s="31">
         <v>5.079E-5</v>
@@ -11546,10 +11542,10 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C381" s="5">
         <v>65357699</v>
@@ -11566,13 +11562,13 @@
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C382" s="5" t="s">
         <v>462</v>
-      </c>
-      <c r="B382" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C382" s="5" t="s">
-        <v>463</v>
       </c>
       <c r="D382" s="31">
         <v>5.079E-5</v>
@@ -11586,10 +11582,10 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C383" s="8">
         <v>198550</v>
@@ -11606,10 +11602,10 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C384" s="5">
         <v>85018</v>
@@ -11626,10 +11622,10 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C385" s="5">
         <v>129000</v>
@@ -11646,10 +11642,10 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B386" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="B386" s="4" t="s">
-        <v>468</v>
       </c>
       <c r="C386" s="5"/>
       <c r="D386" s="31">
@@ -11664,10 +11660,10 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B387" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="B387" s="4" t="s">
-        <v>470</v>
       </c>
       <c r="C387" s="5">
         <v>57976</v>
@@ -11686,10 +11682,10 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B388" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="B388" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="C388" s="5"/>
       <c r="D388" s="31">
@@ -11704,10 +11700,10 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B389" s="4" t="s">
         <v>473</v>
-      </c>
-      <c r="B389" s="4" t="s">
-        <v>474</v>
       </c>
       <c r="C389" s="5">
         <v>42397648</v>
@@ -11726,10 +11722,10 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C390" s="5">
         <v>56495</v>
@@ -11748,10 +11744,10 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C391" s="5">
         <v>7496028</v>
@@ -11770,10 +11766,10 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C392" s="5">
         <v>189640</v>
@@ -11792,10 +11788,10 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C393" s="5">
         <v>189559</v>
@@ -11814,10 +11810,10 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C394" s="5">
         <v>191300</v>
@@ -11836,10 +11832,10 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B395" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="B395" s="4" t="s">
-        <v>481</v>
       </c>
       <c r="C395" s="5"/>
       <c r="D395" s="31">
@@ -11854,10 +11850,10 @@
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B396" s="4" t="s">
         <v>482</v>
-      </c>
-      <c r="B396" s="4" t="s">
-        <v>483</v>
       </c>
       <c r="C396" s="5">
         <v>42397659</v>
@@ -11876,13 +11872,13 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C397" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="B397" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="C397" s="5" t="s">
-        <v>485</v>
       </c>
       <c r="D397" s="4">
         <v>2.1540000000000001E-3</v>
@@ -11896,13 +11892,13 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B398" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="B398" s="4" t="s">
+      <c r="C398" s="5" t="s">
         <v>615</v>
-      </c>
-      <c r="C398" s="5" t="s">
-        <v>616</v>
       </c>
       <c r="D398" s="31">
         <v>1.016E-3</v>
@@ -11916,10 +11912,10 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C399" s="5">
         <v>3697243</v>
@@ -11938,10 +11934,10 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C400" s="5">
         <v>194592</v>
@@ -11960,10 +11956,10 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B401" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="B401" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="C401" s="5">
         <v>50328</v>
@@ -11982,10 +11978,10 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C402" s="5">
         <v>192654</v>
@@ -12004,10 +12000,10 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C403" s="5">
         <v>53703</v>
@@ -12026,13 +12022,13 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C404" s="5" t="s">
         <v>492</v>
-      </c>
-      <c r="B404" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="C404" s="5" t="s">
-        <v>493</v>
       </c>
       <c r="D404" s="31">
         <v>1.016E-3</v>
@@ -12048,10 +12044,10 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B405" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="B405" s="4" t="s">
-        <v>495</v>
       </c>
       <c r="C405" s="5"/>
       <c r="D405" s="31">
@@ -12066,10 +12062,10 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B406" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="B406" s="4" t="s">
-        <v>497</v>
       </c>
       <c r="C406" s="5">
         <v>5522430</v>
@@ -12088,10 +12084,10 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C407" s="5">
         <v>57835924</v>
@@ -12110,10 +12106,10 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C408" s="5">
         <v>602879</v>
@@ -12132,10 +12128,10 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B409" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="B409" s="4" t="s">
-        <v>501</v>
       </c>
       <c r="C409" s="5">
         <v>56553</v>
@@ -12154,10 +12150,10 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C410" s="5">
         <v>205992</v>
@@ -12176,10 +12172,10 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A411" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C411" s="38">
         <v>102</v>
@@ -12196,10 +12192,10 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C412" s="5">
         <v>205823</v>
@@ -12218,10 +12214,10 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C413" s="5">
         <v>226368</v>
@@ -12240,10 +12236,10 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C414" s="5">
         <v>224420</v>
@@ -12262,10 +12258,10 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C415" s="5">
         <v>193395</v>
@@ -12284,10 +12280,10 @@
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B416" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="B416" s="4" t="s">
-        <v>512</v>
       </c>
       <c r="C416" s="5"/>
       <c r="D416" s="31">
@@ -12302,10 +12298,10 @@
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C417" s="5">
         <v>207089</v>
@@ -12324,13 +12320,13 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B418" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="B418" s="4" t="s">
+      <c r="C418" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="C418" s="5" t="s">
-        <v>515</v>
       </c>
       <c r="D418" s="34">
         <v>1.558E-5</v>
@@ -12344,10 +12340,10 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C419" s="5">
         <v>607578</v>
@@ -12366,10 +12362,10 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C420" s="5">
         <v>86748</v>
@@ -12388,16 +12384,16 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C421" s="5">
         <v>218019</v>
       </c>
       <c r="D421" s="40" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E421" s="4">
         <v>0</v>
@@ -12410,10 +12406,10 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B422" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="B422" s="4" t="s">
-        <v>521</v>
       </c>
       <c r="C422" s="5"/>
       <c r="D422" s="31">
@@ -12428,10 +12424,10 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B423" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="B423" s="4" t="s">
-        <v>523</v>
       </c>
       <c r="C423" s="14">
         <v>75</v>
@@ -12448,10 +12444,10 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C424" s="5">
         <v>106503</v>
@@ -12470,10 +12466,10 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C425" s="5">
         <v>123386</v>
@@ -12496,10 +12492,10 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C426" s="5">
         <v>114261</v>
@@ -12518,10 +12514,10 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C427" s="5">
         <v>78875</v>
@@ -12538,10 +12534,10 @@
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C428" s="5">
         <v>75569</v>
@@ -12570,10 +12566,10 @@
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C429" s="5">
         <v>91225</v>
@@ -12592,10 +12588,10 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C430" s="5">
         <v>106514</v>
@@ -12614,10 +12610,10 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C431" s="38">
         <v>605</v>
@@ -12632,13 +12628,13 @@
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C432" s="39" t="s">
         <v>532</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C432" s="39" t="s">
-        <v>533</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -12650,13 +12646,13 @@
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C433" s="38" t="s">
         <v>534</v>
-      </c>
-      <c r="B433" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C433" s="38" t="s">
-        <v>535</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -12668,10 +12664,10 @@
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C434" s="38"/>
       <c r="D434" s="4"/>
@@ -12684,10 +12680,10 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C435" s="38"/>
       <c r="D435" s="4"/>
@@ -12700,10 +12696,10 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C436" s="8">
         <v>7440611</v>
@@ -12720,13 +12716,13 @@
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C437" s="5" t="s">
         <v>539</v>
-      </c>
-      <c r="B437" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C437" s="5" t="s">
-        <v>540</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4">
@@ -12742,10 +12738,10 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C438" s="5">
         <v>7440611</v>
@@ -12764,10 +12760,10 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C439" s="5">
         <v>7783815</v>
@@ -12794,13 +12790,13 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C440" s="5" t="s">
         <v>543</v>
-      </c>
-      <c r="B440" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C440" s="5" t="s">
-        <v>544</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4">
@@ -12816,13 +12812,13 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A441" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C441" s="5" t="s">
         <v>545</v>
-      </c>
-      <c r="B441" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C441" s="5" t="s">
-        <v>546</v>
       </c>
       <c r="D441" s="4">
         <v>0</v>
@@ -12838,13 +12834,13 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B442" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C442" s="5" t="s">
         <v>547</v>
-      </c>
-      <c r="B442" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C442" s="5" t="s">
-        <v>548</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4">
@@ -12858,13 +12854,13 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C443" s="5" t="s">
         <v>549</v>
-      </c>
-      <c r="B443" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C443" s="5" t="s">
-        <v>550</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4">
@@ -12878,10 +12874,10 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="B444" s="4" t="s">
         <v>551</v>
-      </c>
-      <c r="B444" s="4" t="s">
-        <v>552</v>
       </c>
       <c r="C444" s="5">
         <v>7783075</v>
@@ -12904,13 +12900,13 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C445" s="5" t="s">
         <v>553</v>
-      </c>
-      <c r="B445" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C445" s="5" t="s">
-        <v>554</v>
       </c>
       <c r="D445" s="35"/>
       <c r="E445" s="4">
@@ -12924,10 +12920,10 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C446" s="5">
         <v>7783008</v>
@@ -12946,10 +12942,10 @@
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A447" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C447" s="5">
         <v>7782492</v>
@@ -12968,10 +12964,10 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C448" s="5">
         <v>7446084</v>
@@ -12988,13 +12984,13 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C449" s="5" t="s">
         <v>557</v>
-      </c>
-      <c r="B449" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C449" s="5" t="s">
-        <v>558</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4">
@@ -13008,10 +13004,10 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C450" s="5">
         <v>7783791</v>
@@ -13032,10 +13028,10 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C451" s="5">
         <v>12640890</v>
@@ -13052,13 +13048,13 @@
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C452" s="5" t="s">
         <v>561</v>
-      </c>
-      <c r="B452" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C452" s="5" t="s">
-        <v>562</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4">
@@ -13072,13 +13068,13 @@
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B453" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C453" s="5" t="s">
         <v>563</v>
-      </c>
-      <c r="B453" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C453" s="5" t="s">
-        <v>564</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4">
@@ -13092,10 +13088,10 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A454" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C454" s="5">
         <v>630104</v>
@@ -13114,13 +13110,13 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A455" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C455" s="12" t="s">
         <v>566</v>
-      </c>
-      <c r="B455" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C455" s="12" t="s">
-        <v>567</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4">
@@ -13134,13 +13130,13 @@
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A456" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C456" s="12" t="s">
         <v>568</v>
-      </c>
-      <c r="B456" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C456" s="12" t="s">
-        <v>569</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4">
@@ -13154,10 +13150,10 @@
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A457" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C457" s="5">
         <v>100425</v>
@@ -13186,10 +13182,10 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A458" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C458" s="5">
         <v>96093</v>
@@ -13206,10 +13202,10 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A459" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C459" s="5">
         <v>127184</v>
@@ -13238,10 +13234,10 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C460" s="5">
         <v>7550450</v>
@@ -13266,10 +13262,10 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C461" s="5">
         <v>108883</v>
@@ -13296,10 +13292,10 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A462" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C462" s="5">
         <v>8001352</v>
@@ -13318,10 +13314,10 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A463" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C463" s="5">
         <v>79016</v>
@@ -13348,10 +13344,10 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A464" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C464" s="5">
         <v>121448</v>
@@ -13372,10 +13368,10 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C465" s="5">
         <v>1582098</v>
@@ -13392,10 +13388,10 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C466" s="5">
         <v>108054</v>
@@ -13422,10 +13418,10 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A467" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C467" s="5">
         <v>593602</v>
@@ -13444,10 +13440,10 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C468" s="5">
         <v>75014</v>
@@ -13476,10 +13472,10 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A469" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C469" s="5">
         <v>75354</v>
@@ -13500,10 +13496,10 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A470" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B470" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="B470" s="4" t="s">
-        <v>584</v>
       </c>
       <c r="C470" s="5">
         <v>108383</v>
@@ -13524,10 +13520,10 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A471" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C471" s="5">
         <v>95476</v>
@@ -13548,10 +13544,10 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A472" s="21" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B472" s="21" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C472" s="20">
         <v>106423</v>
@@ -13572,10 +13568,10 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A473" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C473" s="5">
         <v>1330207</v>
@@ -13600,13 +13596,13 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A474" s="22" t="s">
+        <v>587</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C474" s="5" t="s">
         <v>588</v>
-      </c>
-      <c r="B474" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="C474" s="5" t="s">
-        <v>589</v>
       </c>
       <c r="D474" s="4"/>
       <c r="E474" s="4"/>
@@ -13618,10 +13614,10 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A475" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B475" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="B475" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="C475" s="12">
         <v>67425</v>
@@ -13638,13 +13634,13 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A476" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C476" s="12" t="s">
         <v>269</v>
-      </c>
-      <c r="B476" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C476" s="12" t="s">
-        <v>270</v>
       </c>
       <c r="D476" s="4"/>
       <c r="E476" s="4"/>
@@ -13656,10 +13652,10 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C477" s="5">
         <v>1589497</v>
@@ -13674,10 +13670,10 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C478" s="5">
         <v>16672392</v>
@@ -13692,10 +13688,10 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A479" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C479" s="8">
         <v>120558</v>
@@ -13710,13 +13706,13 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A480" s="18" t="s">
+        <v>607</v>
+      </c>
+      <c r="B480" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C480" s="19" t="s">
         <v>608</v>
-      </c>
-      <c r="B480" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C480" s="19" t="s">
-        <v>609</v>
       </c>
       <c r="D480" s="4"/>
       <c r="E480" s="4"/>
@@ -13728,13 +13724,13 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B481" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C481" s="5" t="s">
         <v>293</v>
-      </c>
-      <c r="B481" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C481" s="5" t="s">
-        <v>294</v>
       </c>
       <c r="D481" s="4"/>
       <c r="E481" s="4"/>
@@ -13746,7 +13742,7 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B482" s="4"/>
       <c r="C482" s="5"/>
@@ -13760,7 +13756,7 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A483" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B483" s="4"/>
       <c r="C483" s="5"/>
@@ -13774,7 +13770,7 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A484" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B484" s="4"/>
       <c r="C484" s="5"/>
@@ -13788,7 +13784,7 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A485" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B485" s="4"/>
       <c r="C485" s="5"/>
@@ -13802,7 +13798,7 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B486" s="4"/>
       <c r="C486" s="5"/>
@@ -13816,7 +13812,7 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B487" s="4"/>
       <c r="C487" s="5"/>
@@ -13830,7 +13826,7 @@
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B488" s="4"/>
       <c r="C488" s="5"/>
@@ -13844,7 +13840,7 @@
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B489" s="4"/>
       <c r="C489" s="5"/>
@@ -13858,7 +13854,7 @@
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A490" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B490" s="4"/>
       <c r="C490" s="5"/>
@@ -13872,7 +13868,7 @@
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A491" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B491" s="4"/>
       <c r="C491" s="5"/>
@@ -13886,7 +13882,7 @@
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B492" s="4"/>
       <c r="C492" s="5"/>
@@ -13900,7 +13896,7 @@
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B493" s="4"/>
       <c r="C493" s="5"/>
@@ -13914,7 +13910,7 @@
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A494" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B494" s="4"/>
       <c r="C494" s="5"/>
@@ -13928,7 +13924,7 @@
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A495" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B495" s="4"/>
       <c r="C495" s="5"/>
@@ -13942,7 +13938,7 @@
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A496" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B496" s="4"/>
       <c r="C496" s="5"/>
@@ -13956,7 +13952,7 @@
     </row>
     <row r="497" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B497" s="4"/>
       <c r="C497" s="5"/>
@@ -13970,7 +13966,7 @@
     </row>
     <row r="498" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A498" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B498" s="4"/>
       <c r="D498" s="4"/>
@@ -13983,7 +13979,7 @@
     </row>
     <row r="499" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A499" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B499" s="4"/>
       <c r="C499" s="5"/>

--- a/resources/Dose_Response_Library.xlsx
+++ b/resources/Dose_Response_Library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_HEM4\HEM4\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8EA491-702F-4ABF-A6CD-FFA881D04658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506C743B-508F-4D36-9B38-AF7495FC9485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1959,11 +1959,11 @@
     <t>106-94-5</t>
   </si>
   <si>
-    <t>Acute NCREL
+    <t>ERPG-2
 (mg/m3)</t>
   </si>
   <si>
-    <t>NCERPG-2
+    <t>Acute REL
 (mg/m3)</t>
   </si>
 </sst>
@@ -3010,10 +3010,10 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>630</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">

--- a/resources/Dose_Response_Library.xlsx
+++ b/resources/Dose_Response_Library.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_HEM4\HEM4\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scainccloud-my.sharepoint.com/personal/jmozier_scainc_com/Documents/Projects/ASRA-RIS-BasePeriod/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506C743B-508F-4D36-9B38-AF7495FC9485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DF64BD5-AAA7-4B3A-9E76-99ABBD218580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2100" yWindow="1500" windowWidth="26700" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dose Response Value Library" sheetId="1" r:id="rId1"/>
@@ -82,6 +82,10 @@
 (mg/m3)</t>
   </si>
   <si>
+    <t>ERPG-2
+(mg/m3)</t>
+  </si>
+  <si>
     <t>1,1,1-Trichloroethane</t>
   </si>
   <si>
@@ -1953,18 +1957,14 @@
     </r>
   </si>
   <si>
-    <t>1-Bromopropane</t>
-  </si>
-  <si>
-    <t>106-94-5</t>
-  </si>
-  <si>
-    <t>ERPG-2
-(mg/m3)</t>
-  </si>
-  <si>
     <t>Acute REL
 (mg/m3)</t>
+  </si>
+  <si>
+    <t>1-Bromopropane</t>
+  </si>
+  <si>
+    <t>106-94-5</t>
   </si>
 </sst>
 </file>
@@ -2969,22 +2969,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J499"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.77734375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" customWidth="1"/>
     <col min="3" max="3" width="14" style="26" customWidth="1"/>
     <col min="4" max="4" width="21" style="6" customWidth="1"/>
     <col min="5" max="5" width="11" style="6" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="27" customWidth="1"/>
-    <col min="7" max="7" width="9.21875" style="27" customWidth="1"/>
-    <col min="8" max="8" width="9.77734375" style="27" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" style="27" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="27" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" style="27" customWidth="1"/>
     <col min="10" max="10" width="12" style="27" customWidth="1"/>
-    <col min="11" max="16384" width="9.21875" style="6"/>
+    <col min="11" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -3010,18 +3010,18 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>629</v>
+        <v>7</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5">
         <v>71556</v>
@@ -3048,12 +3048,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5">
         <v>79345</v>
@@ -3068,12 +3068,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5">
         <v>79005</v>
@@ -3088,12 +3088,12 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5">
         <v>57147</v>
@@ -3112,12 +3112,12 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="5">
         <v>319846</v>
@@ -3132,12 +3132,12 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="C7" s="5">
         <v>319857</v>
@@ -3152,12 +3152,12 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5">
         <v>58899</v>
@@ -3172,12 +3172,12 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="5">
         <v>608731</v>
@@ -3194,12 +3194,12 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="5">
         <v>120821</v>
@@ -3216,12 +3216,12 @@
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5">
         <v>96128</v>
@@ -3238,12 +3238,12 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5">
         <v>122667</v>
@@ -3260,12 +3260,12 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="5">
         <v>106887</v>
@@ -3286,12 +3286,12 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" s="5">
         <v>75558</v>
@@ -3310,12 +3310,12 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="5">
         <v>106990</v>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" s="5">
         <v>542756</v>
@@ -3362,12 +3362,12 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="5">
         <v>1120714</v>
@@ -3384,12 +3384,12 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" s="5">
         <v>106467</v>
@@ -3406,12 +3406,12 @@
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="5">
         <v>60117</v>
@@ -3428,12 +3428,12 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="5">
         <v>123911</v>
@@ -3456,15 +3456,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D21" s="4">
         <v>9.9999999999999995E-7</v>
@@ -3476,12 +3476,12 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" s="8">
         <v>540841</v>
@@ -3494,12 +3494,12 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="5">
         <v>95954</v>
@@ -3516,12 +3516,12 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="5">
         <v>88062</v>
@@ -3538,12 +3538,12 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" s="5">
         <v>94757</v>
@@ -3560,12 +3560,12 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="5">
         <v>51285</v>
@@ -3582,12 +3582,12 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>25321146</v>
@@ -3602,12 +3602,12 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="5">
         <v>121142</v>
@@ -3622,12 +3622,12 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="5">
         <v>95807</v>
@@ -3644,12 +3644,12 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30" s="5">
         <v>26471625</v>
@@ -3676,12 +3676,12 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="5">
         <v>584849</v>
@@ -3708,12 +3708,12 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32" s="5">
         <v>532274</v>
@@ -3728,12 +3728,12 @@
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C33" s="5">
         <v>79469</v>
@@ -3750,12 +3750,12 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C34" s="5">
         <v>91941</v>
@@ -3772,12 +3772,12 @@
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" s="5">
         <v>119904</v>
@@ -3792,12 +3792,12 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C36" s="5">
         <v>119937</v>
@@ -3812,12 +3812,12 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C37" s="5">
         <v>101144</v>
@@ -3834,12 +3834,12 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C38" s="5">
         <v>101779</v>
@@ -3856,12 +3856,12 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" s="5">
         <v>101688</v>
@@ -3882,12 +3882,12 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40" s="5">
         <v>534521</v>
@@ -3904,12 +3904,12 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C41" s="8">
         <v>92671</v>
@@ -3922,12 +3922,12 @@
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C42" s="8">
         <v>92933</v>
@@ -3940,12 +3940,12 @@
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" s="5">
         <v>100027</v>
@@ -3962,12 +3962,12 @@
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C44" s="5">
         <v>75070</v>
@@ -3994,12 +3994,12 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C45" s="5">
         <v>60355</v>
@@ -4016,12 +4016,12 @@
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C46" s="5">
         <v>75058</v>
@@ -4042,12 +4042,12 @@
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C47" s="5">
         <v>98862</v>
@@ -4064,12 +4064,12 @@
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C48" s="10">
         <v>107028</v>
@@ -4096,12 +4096,12 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C49" s="5">
         <v>79061</v>
@@ -4118,12 +4118,12 @@
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C50" s="5">
         <v>79107</v>
@@ -4150,12 +4150,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C51" s="5">
         <v>107131</v>
@@ -4178,12 +4178,12 @@
       </c>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C52" s="5">
         <v>107051</v>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C53" s="5">
         <v>62533</v>
@@ -4234,12 +4234,12 @@
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C54" s="5">
         <v>90040</v>
@@ -4256,12 +4256,12 @@
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C55" s="5">
         <v>7440360</v>
@@ -4278,12 +4278,12 @@
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="C56" s="5">
         <v>1327339</v>
@@ -4298,15 +4298,15 @@
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4">
@@ -4318,12 +4318,12 @@
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C58" s="5">
         <v>1314609</v>
@@ -4340,12 +4340,12 @@
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C59" s="5">
         <v>304610</v>
@@ -4362,12 +4362,12 @@
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" s="5">
         <v>1332816</v>
@@ -4384,15 +4384,15 @@
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C62" s="5">
         <v>1309644</v>
@@ -4430,12 +4430,12 @@
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C63" s="5">
         <v>7778394</v>
@@ -4454,12 +4454,12 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="C64" s="8">
         <v>7784409</v>
@@ -4478,15 +4478,15 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D65" s="4">
         <v>4.3E-3</v>
@@ -4502,15 +4502,15 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D66" s="15">
         <v>4.3E-3</v>
@@ -4528,15 +4528,15 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D67" s="4">
         <v>4.3E-3</v>
@@ -4552,12 +4552,12 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C68" s="5">
         <v>1327533</v>
@@ -4578,12 +4578,12 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C69" s="5">
         <v>7784421</v>
@@ -4604,12 +4604,12 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C70" s="5">
         <v>71432</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="J70" s="4"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C71" s="5">
         <v>92875</v>
@@ -4654,12 +4654,12 @@
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C72" s="5">
         <v>98077</v>
@@ -4674,12 +4674,12 @@
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C73" s="5">
         <v>100447</v>
@@ -4702,15 +4702,15 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D74" s="4">
         <v>2.3999999999999998E-3</v>
@@ -4724,12 +4724,12 @@
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C75" s="5">
         <v>7440417</v>
@@ -4748,15 +4748,15 @@
       </c>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D76" s="4">
         <v>2.3999999999999998E-3</v>
@@ -4770,15 +4770,15 @@
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D77" s="4">
         <v>2.3999999999999998E-3</v>
@@ -4792,15 +4792,15 @@
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D78" s="4">
         <v>2.3999999999999998E-3</v>
@@ -4814,12 +4814,12 @@
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C79" s="5">
         <v>57578</v>
@@ -4832,12 +4832,12 @@
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C80" s="5">
         <v>92524</v>
@@ -4856,12 +4856,12 @@
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C81" s="5">
         <v>117817</v>
@@ -4876,12 +4876,12 @@
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C82" s="5">
         <v>542881</v>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="J82" s="4"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C83" s="5">
         <v>75252</v>
@@ -4924,12 +4924,12 @@
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C84" s="8">
         <v>543908</v>
@@ -4946,12 +4946,12 @@
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C85" s="5">
         <v>7440439</v>
@@ -4972,15 +4972,15 @@
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="C86" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D86" s="4">
         <v>1.8E-3</v>
@@ -4994,12 +4994,12 @@
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C87" s="5">
         <v>10325947</v>
@@ -5016,12 +5016,12 @@
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C88" s="8">
         <v>1306190</v>
@@ -5038,15 +5038,15 @@
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D89" s="4">
         <v>1.8E-3</v>
@@ -5060,12 +5060,12 @@
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C90" s="5">
         <v>133062</v>
@@ -5080,12 +5080,12 @@
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C91" s="5">
         <v>63252</v>
@@ -5102,12 +5102,12 @@
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C92" s="5">
         <v>75150</v>
@@ -5134,12 +5134,12 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C93" s="5">
         <v>56235</v>
@@ -5164,12 +5164,12 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C94" s="8">
         <v>463581</v>
@@ -5186,12 +5186,12 @@
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C95" s="8">
         <v>120809</v>
@@ -5204,12 +5204,12 @@
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C96" s="5">
         <v>133904</v>
@@ -5226,12 +5226,12 @@
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C97" s="5">
         <v>57749</v>
@@ -5248,12 +5248,12 @@
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C98" s="5">
         <v>7782505</v>
@@ -5280,12 +5280,12 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C99" s="5">
         <v>79118</v>
@@ -5304,12 +5304,12 @@
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C100" s="5">
         <v>108907</v>
@@ -5330,12 +5330,12 @@
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C101" s="5">
         <v>510156</v>
@@ -5352,12 +5352,12 @@
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C102" s="5">
         <v>67663</v>
@@ -5380,12 +5380,12 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C103" s="5">
         <v>107302</v>
@@ -5406,12 +5406,12 @@
       </c>
       <c r="J103" s="4"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C104" s="5">
         <v>126998</v>
@@ -5428,12 +5428,12 @@
       <c r="I104" s="4"/>
       <c r="J104" s="4"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C105" s="8">
         <v>7788989</v>
@@ -5450,12 +5450,12 @@
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B106" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="C106" s="8">
         <v>7789095</v>
@@ -5472,12 +5472,12 @@
       <c r="I106" s="4"/>
       <c r="J106" s="4"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C107" s="8">
         <v>10294403</v>
@@ -5494,12 +5494,12 @@
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C108" s="28">
         <v>13765190</v>
@@ -5516,15 +5516,15 @@
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C109" s="30" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D109" s="4">
         <v>1.839E-2</v>
@@ -5538,12 +5538,12 @@
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C110" s="5">
         <v>1308389</v>
@@ -5556,12 +5556,12 @@
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C111" s="5">
         <v>10101538</v>
@@ -5574,12 +5574,12 @@
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C112" s="5">
         <v>13530682</v>
@@ -5596,12 +5596,12 @@
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C113" s="5">
         <v>16065831</v>
@@ -5618,12 +5618,12 @@
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C114" s="8">
         <v>7758976</v>
@@ -5640,12 +5640,12 @@
       <c r="I114" s="4"/>
       <c r="J114" s="4"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C115" s="28">
         <v>18454121</v>
@@ -5662,12 +5662,12 @@
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C116" s="5">
         <v>18540299</v>
@@ -5684,12 +5684,12 @@
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C117" s="5">
         <v>11115745</v>
@@ -5706,15 +5706,15 @@
       <c r="I117" s="4"/>
       <c r="J117" s="4"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -5724,12 +5724,12 @@
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C119" s="5">
         <v>7440473</v>
@@ -5746,12 +5746,12 @@
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C120" s="5">
         <v>12018018</v>
@@ -5768,12 +5768,12 @@
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C121" s="5">
         <v>12018198</v>
@@ -5786,12 +5786,12 @@
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C122" s="5">
         <v>7789006</v>
@@ -5808,12 +5808,12 @@
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C123" s="5">
         <v>7778509</v>
@@ -5830,12 +5830,12 @@
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C124" s="8">
         <v>7775113</v>
@@ -5852,12 +5852,12 @@
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C125" s="8">
         <v>10588019</v>
@@ -5874,12 +5874,12 @@
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C126" s="8">
         <v>7789062</v>
@@ -5896,12 +5896,12 @@
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C127" s="28">
         <v>13530659</v>
@@ -5918,12 +5918,12 @@
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C128" s="28">
         <v>50922297</v>
@@ -5936,12 +5936,12 @@
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C129" s="8">
         <v>11103869</v>
@@ -5958,12 +5958,12 @@
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C130" s="5">
         <v>1345160</v>
@@ -5978,15 +5978,15 @@
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B131" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B131" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="C131" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="4">
@@ -5998,15 +5998,15 @@
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4">
@@ -6018,15 +6018,15 @@
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4">
@@ -6038,15 +6038,15 @@
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4">
@@ -6058,12 +6058,12 @@
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C135" s="5">
         <v>7440484</v>
@@ -6080,15 +6080,15 @@
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="J136" s="4"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C137" s="5">
         <v>61789513</v>
@@ -6122,15 +6122,15 @@
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4">
@@ -6142,12 +6142,12 @@
       <c r="I138" s="4"/>
       <c r="J138" s="4"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C139" s="5">
         <v>1307966</v>
@@ -6162,12 +6162,12 @@
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C140" s="5">
         <v>1308061</v>
@@ -6182,12 +6182,12 @@
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
     </row>
-    <row r="141" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C141" s="5">
         <v>136527</v>
@@ -6202,12 +6202,12 @@
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C142" s="14">
         <v>141</v>
@@ -6222,12 +6222,12 @@
       <c r="I142" s="4"/>
       <c r="J142" s="4"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C143" s="5">
         <v>8007452</v>
@@ -6242,12 +6242,12 @@
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B144" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="C144" s="5">
         <v>8007452</v>
@@ -6264,12 +6264,12 @@
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C145" s="14">
         <v>142</v>
@@ -6284,12 +6284,12 @@
       <c r="I145" s="4"/>
       <c r="J145" s="4"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C146" s="5">
         <v>1319773</v>
@@ -6306,12 +6306,12 @@
       <c r="I146" s="4"/>
       <c r="J146" s="4"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="C147" s="5">
         <v>108394</v>
@@ -6328,12 +6328,12 @@
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C148" s="5">
         <v>95487</v>
@@ -6350,12 +6350,12 @@
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C149" s="5">
         <v>106445</v>
@@ -6372,12 +6372,12 @@
       <c r="I149" s="4"/>
       <c r="J149" s="4"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C150" s="5">
         <v>98828</v>
@@ -6398,12 +6398,12 @@
       <c r="I150" s="4"/>
       <c r="J150" s="4"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C151" s="5">
         <v>75865</v>
@@ -6424,15 +6424,15 @@
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B152" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B152" s="4" t="s">
-        <v>185</v>
-      </c>
       <c r="C152" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4">
@@ -6444,15 +6444,15 @@
       <c r="I152" s="4"/>
       <c r="J152" s="4"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4">
@@ -6464,12 +6464,12 @@
       <c r="I153" s="4"/>
       <c r="J153" s="4"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C154" s="5">
         <v>592018</v>
@@ -6490,12 +6490,12 @@
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C155" s="5">
         <v>544923</v>
@@ -6512,12 +6512,12 @@
       <c r="I155" s="4"/>
       <c r="J155" s="4"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C156" s="5">
         <v>21725462</v>
@@ -6532,15 +6532,15 @@
       <c r="I156" s="4"/>
       <c r="J156" s="4"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4">
@@ -6552,12 +6552,12 @@
       <c r="I157" s="4"/>
       <c r="J157" s="4"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C158" s="5">
         <v>57125</v>
@@ -6574,12 +6574,12 @@
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C159" s="5">
         <v>460195</v>
@@ -6600,12 +6600,12 @@
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C160" s="5">
         <v>506683</v>
@@ -6622,12 +6622,12 @@
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C161" s="5">
         <v>506774</v>
@@ -6646,15 +6646,15 @@
       </c>
       <c r="J161" s="4"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4">
@@ -6666,15 +6666,15 @@
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4">
@@ -6686,15 +6686,15 @@
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4">
@@ -6706,12 +6706,12 @@
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C165" s="5">
         <v>109784</v>
@@ -6728,12 +6728,12 @@
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C166" s="5">
         <v>74908</v>
@@ -6758,12 +6758,12 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C167" s="8">
         <v>78820</v>
@@ -6784,12 +6784,12 @@
       </c>
       <c r="J167" s="4"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C168" s="5">
         <v>151508</v>
@@ -6810,12 +6810,12 @@
       <c r="I168" s="4"/>
       <c r="J168" s="4"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C169" s="5">
         <v>506616</v>
@@ -6832,15 +6832,15 @@
       <c r="I169" s="4"/>
       <c r="J169" s="4"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4">
@@ -6852,12 +6852,12 @@
       <c r="I170" s="4"/>
       <c r="J170" s="4"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C171" s="5">
         <v>506649</v>
@@ -6874,12 +6874,12 @@
       <c r="I171" s="4"/>
       <c r="J171" s="4"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C172" s="5">
         <v>143339</v>
@@ -6900,15 +6900,15 @@
       <c r="I172" s="4"/>
       <c r="J172" s="4"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D173" s="4">
         <v>0</v>
@@ -6922,12 +6922,12 @@
       <c r="I173" s="4"/>
       <c r="J173" s="4"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C174" s="5">
         <v>21564170</v>
@@ -6944,12 +6944,12 @@
       <c r="I174" s="4"/>
       <c r="J174" s="4"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C175" s="5">
         <v>557211</v>
@@ -6966,12 +6966,12 @@
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C176" s="5">
         <v>72559</v>
@@ -6986,15 +6986,15 @@
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -7004,12 +7004,12 @@
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C178" s="5">
         <v>132649</v>
@@ -7026,12 +7026,12 @@
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C179" s="5">
         <v>84742</v>
@@ -7048,12 +7048,12 @@
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C180" s="5">
         <v>111444</v>
@@ -7070,12 +7070,12 @@
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C181" s="5">
         <v>62737</v>
@@ -7094,15 +7094,15 @@
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D182" s="4">
         <v>0</v>
@@ -7116,12 +7116,12 @@
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C183" s="5">
         <v>111422</v>
@@ -7138,12 +7138,12 @@
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C184" s="8">
         <v>64675</v>
@@ -7156,12 +7156,12 @@
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C185" s="5">
         <v>68122</v>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="J185" s="4"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C186" s="5">
         <v>131113</v>
@@ -7206,12 +7206,12 @@
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C187" s="5">
         <v>77781</v>
@@ -7232,12 +7232,12 @@
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A188" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C188" s="8">
         <v>79447</v>
@@ -7250,12 +7250,12 @@
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C189" s="5">
         <v>3268879</v>
@@ -7272,12 +7272,12 @@
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C190" s="5">
         <v>39001020</v>
@@ -7294,12 +7294,12 @@
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C191" s="5">
         <v>35822469</v>
@@ -7316,12 +7316,12 @@
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C192" s="5">
         <v>67562394</v>
@@ -7338,12 +7338,12 @@
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C193" s="5">
         <v>55673897</v>
@@ -7360,12 +7360,12 @@
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C194" s="5">
         <v>39227286</v>
@@ -7382,12 +7382,12 @@
       <c r="I194" s="4"/>
       <c r="J194" s="4"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C195" s="5">
         <v>70648269</v>
@@ -7404,12 +7404,12 @@
       <c r="I195" s="4"/>
       <c r="J195" s="4"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C196" s="5">
         <v>57653857</v>
@@ -7426,12 +7426,12 @@
       <c r="I196" s="4"/>
       <c r="J196" s="4"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C197" s="5">
         <v>57117449</v>
@@ -7448,12 +7448,12 @@
       <c r="I197" s="4"/>
       <c r="J197" s="4"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C198" s="5">
         <v>19408743</v>
@@ -7470,12 +7470,12 @@
       <c r="I198" s="4"/>
       <c r="J198" s="4"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C199" s="5">
         <v>72918219</v>
@@ -7492,12 +7492,12 @@
       <c r="I199" s="4"/>
       <c r="J199" s="4"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C200" s="5">
         <v>40321764</v>
@@ -7514,12 +7514,12 @@
       <c r="I200" s="4"/>
       <c r="J200" s="4"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C201" s="5">
         <v>57117416</v>
@@ -7536,12 +7536,12 @@
       <c r="I201" s="4"/>
       <c r="J201" s="4"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C202" s="5">
         <v>60851345</v>
@@ -7558,12 +7558,12 @@
       <c r="I202" s="4"/>
       <c r="J202" s="4"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C203" s="5">
         <v>57117314</v>
@@ -7580,12 +7580,12 @@
       <c r="I203" s="4"/>
       <c r="J203" s="4"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C204" s="5">
         <v>1746016</v>
@@ -7602,12 +7602,12 @@
       <c r="I204" s="4"/>
       <c r="J204" s="4"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C205" s="5">
         <v>51207319</v>
@@ -7624,12 +7624,12 @@
       <c r="I205" s="4"/>
       <c r="J205" s="4"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B206" s="32" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C206" s="5">
         <v>34465468</v>
@@ -7646,12 +7646,12 @@
       <c r="I206" s="4"/>
       <c r="J206" s="4"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B207" s="32" t="s">
         <v>251</v>
-      </c>
-      <c r="B207" s="32" t="s">
-        <v>250</v>
       </c>
       <c r="C207" s="5">
         <v>136677106</v>
@@ -7664,12 +7664,12 @@
       <c r="I207" s="4"/>
       <c r="J207" s="4"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C208" s="5">
         <v>106898</v>
@@ -7696,12 +7696,12 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C209" s="5">
         <v>140885</v>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="J209" s="4"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C210" s="5">
         <v>100414</v>
@@ -7750,12 +7750,12 @@
       <c r="I210" s="4"/>
       <c r="J210" s="4"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C211" s="5">
         <v>51796</v>
@@ -7772,12 +7772,12 @@
       <c r="I211" s="4"/>
       <c r="J211" s="4"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A212" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C212" s="5">
         <v>75003</v>
@@ -7794,12 +7794,12 @@
       <c r="I212" s="4"/>
       <c r="J212" s="4"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C213" s="5">
         <v>106934</v>
@@ -7820,12 +7820,12 @@
       <c r="I213" s="4"/>
       <c r="J213" s="4"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C214" s="5">
         <v>107062</v>
@@ -7846,12 +7846,12 @@
       </c>
       <c r="J214" s="4"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C215" s="5">
         <v>107211</v>
@@ -7868,12 +7868,12 @@
       <c r="I215" s="4"/>
       <c r="J215" s="4"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C216" s="5">
         <v>151564</v>
@@ -7892,12 +7892,12 @@
       <c r="I216" s="4"/>
       <c r="J216" s="4"/>
     </row>
-    <row r="217" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C217" s="5">
         <v>75218</v>
@@ -7918,12 +7918,12 @@
       </c>
       <c r="J217" s="4"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C218" s="5">
         <v>96457</v>
@@ -7938,12 +7938,12 @@
       <c r="I218" s="4"/>
       <c r="J218" s="4"/>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A219" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C219" s="5">
         <v>75343</v>
@@ -7960,12 +7960,12 @@
       <c r="I219" s="4"/>
       <c r="J219" s="4"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C220" s="5">
         <v>50000</v>
@@ -7992,12 +7992,12 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A221" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B221" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="B221" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="C221" s="8">
         <v>110714</v>
@@ -8016,12 +8016,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A222" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C222" s="8">
         <v>112072</v>
@@ -8040,12 +8040,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A223" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C223" s="8">
         <v>112254</v>
@@ -8064,12 +8064,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A224" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C224" s="8">
         <v>20706256</v>
@@ -8086,12 +8086,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A225" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C225" s="8">
         <v>124174</v>
@@ -8110,12 +8110,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C226" s="5">
         <v>112152</v>
@@ -8132,12 +8132,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A227" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C227" s="8">
         <v>112367</v>
@@ -8154,12 +8154,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A228" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C228" s="8">
         <v>111966</v>
@@ -8178,12 +8178,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A229" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C229" s="8">
         <v>1002671</v>
@@ -8200,12 +8200,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C230" s="5">
         <v>112345</v>
@@ -8224,12 +8224,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A231" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C231" s="5">
         <v>111900</v>
@@ -8248,12 +8248,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A232" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C232" s="8">
         <v>111773</v>
@@ -8272,15 +8272,15 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A233" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C233" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="4">
@@ -8294,12 +8294,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C234" s="5">
         <v>629141</v>
@@ -8316,12 +8316,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C235" s="5">
         <v>110805</v>
@@ -8340,12 +8340,12 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C236" s="5">
         <v>111159</v>
@@ -8364,12 +8364,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C237" s="5">
         <v>109864</v>
@@ -8388,12 +8388,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C238" s="5">
         <v>110496</v>
@@ -8412,12 +8412,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C239" s="5">
         <v>7795917</v>
@@ -8434,12 +8434,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A240" s="18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C240" s="18">
         <v>171</v>
@@ -8458,12 +8458,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A241" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C241" s="8">
         <v>112356</v>
@@ -8482,15 +8482,15 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A242" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D242" s="4"/>
       <c r="E242" s="4">
@@ -8504,12 +8504,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A243" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C243" s="8">
         <v>112594</v>
@@ -8528,12 +8528,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A244" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C244" s="8">
         <v>122996</v>
@@ -8552,12 +8552,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A245" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C245" s="8">
         <v>2807309</v>
@@ -8576,12 +8576,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A246" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C246" s="8">
         <v>112492</v>
@@ -8598,15 +8598,15 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A247" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="4">
@@ -8620,12 +8620,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C248" s="5">
         <v>143226</v>
@@ -8642,12 +8642,12 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C249" s="5">
         <v>76448</v>
@@ -8664,12 +8664,12 @@
       <c r="I249" s="4"/>
       <c r="J249" s="4"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C250" s="5">
         <v>118741</v>
@@ -8684,12 +8684,12 @@
       <c r="I250" s="4"/>
       <c r="J250" s="4"/>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C251" s="5">
         <v>87683</v>
@@ -8708,12 +8708,12 @@
       </c>
       <c r="J251" s="4"/>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C252" s="5">
         <v>77474</v>
@@ -8730,12 +8730,12 @@
       <c r="I252" s="4"/>
       <c r="J252" s="4"/>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C253" s="5">
         <v>67721</v>
@@ -8750,12 +8750,12 @@
       <c r="I253" s="4"/>
       <c r="J253" s="4"/>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C254" s="5">
         <v>822060</v>
@@ -8772,12 +8772,12 @@
       <c r="I254" s="4"/>
       <c r="J254" s="4"/>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C255" s="5">
         <v>680319</v>
@@ -8790,12 +8790,12 @@
       <c r="I255" s="4"/>
       <c r="J255" s="4"/>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C256" s="5">
         <v>110543</v>
@@ -8814,12 +8814,12 @@
       <c r="I256" s="4"/>
       <c r="J256" s="4"/>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C257" s="5">
         <v>302012</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="J257" s="4"/>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C258" s="5">
         <v>7647010</v>
@@ -8876,12 +8876,12 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C259" s="5">
         <v>7664393</v>
@@ -8908,12 +8908,12 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C260" s="5">
         <v>123319</v>
@@ -8930,12 +8930,12 @@
       <c r="I260" s="4"/>
       <c r="J260" s="4"/>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C261" s="5">
         <v>78591</v>
@@ -8950,12 +8950,12 @@
       <c r="I261" s="4"/>
       <c r="J261" s="4"/>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A262" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C262" s="8">
         <v>1317368</v>
@@ -8970,12 +8970,12 @@
       <c r="I262" s="4"/>
       <c r="J262" s="4"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A263" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B263" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="B263" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="C263" s="8">
         <v>301042</v>
@@ -8990,12 +8990,12 @@
       <c r="I263" s="4"/>
       <c r="J263" s="4"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A264" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C264" s="8">
         <v>7784409</v>
@@ -9012,12 +9012,12 @@
       <c r="I264" s="4"/>
       <c r="J264" s="4"/>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A265" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C265" s="8">
         <v>7758976</v>
@@ -9034,12 +9034,12 @@
       <c r="I265" s="4"/>
       <c r="J265" s="4"/>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A266" s="18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C266" s="28">
         <v>18454121</v>
@@ -9056,15 +9056,15 @@
       <c r="I266" s="4"/>
       <c r="J266" s="4"/>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A267" s="18" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C267" s="30" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D267" s="4"/>
       <c r="E267" s="4">
@@ -9076,12 +9076,12 @@
       <c r="I267" s="4"/>
       <c r="J267" s="4"/>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C268" s="5">
         <v>7439921</v>
@@ -9098,12 +9098,12 @@
       <c r="I268" s="4"/>
       <c r="J268" s="4"/>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C269" s="14">
         <v>603</v>
@@ -9118,12 +9118,12 @@
       <c r="I269" s="4"/>
       <c r="J269" s="4"/>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A270" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C270" s="8">
         <v>1309600</v>
@@ -9140,12 +9140,12 @@
       <c r="I270" s="4"/>
       <c r="J270" s="4"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A271" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C271" s="8">
         <v>10099748</v>
@@ -9160,12 +9160,12 @@
       <c r="I271" s="4"/>
       <c r="J271" s="4"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A272" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C272" s="8">
         <v>1335326</v>
@@ -9180,12 +9180,12 @@
       <c r="I272" s="4"/>
       <c r="J272" s="4"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A273" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C273" s="8">
         <v>7446142</v>
@@ -9200,12 +9200,12 @@
       <c r="I273" s="4"/>
       <c r="J273" s="4"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C274" s="5">
         <v>78002</v>
@@ -9222,12 +9222,12 @@
       <c r="I274" s="4"/>
       <c r="J274" s="4"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C275" s="5">
         <v>75741</v>
@@ -9244,12 +9244,12 @@
       <c r="I275" s="4"/>
       <c r="J275" s="4"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C276" s="5">
         <v>108316</v>
@@ -9270,12 +9270,12 @@
       </c>
       <c r="J276" s="4"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C277" s="5">
         <v>2145076</v>
@@ -9290,12 +9290,12 @@
       <c r="I277" s="4"/>
       <c r="J277" s="4"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C278" s="5">
         <v>7439965</v>
@@ -9312,12 +9312,12 @@
       <c r="I278" s="4"/>
       <c r="J278" s="4"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A279" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B279" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="B279" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="C279" s="8">
         <v>1313139</v>
@@ -9334,12 +9334,12 @@
       <c r="I279" s="4"/>
       <c r="J279" s="4"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A280" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C280" s="8">
         <v>10377669</v>
@@ -9354,15 +9354,15 @@
       <c r="I280" s="4"/>
       <c r="J280" s="4"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A281" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D281" s="4"/>
       <c r="E281" s="4">
@@ -9374,12 +9374,12 @@
       <c r="I281" s="4"/>
       <c r="J281" s="4"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A282" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C282" s="8">
         <v>7785877</v>
@@ -9396,12 +9396,12 @@
       <c r="I282" s="4"/>
       <c r="J282" s="4"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A283" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C283" s="8">
         <v>1317357</v>
@@ -9416,12 +9416,12 @@
       <c r="I283" s="4"/>
       <c r="J283" s="4"/>
     </row>
-    <row r="284" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A284" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C284" s="8">
         <v>12079651</v>
@@ -9436,12 +9436,12 @@
       <c r="I284" s="4"/>
       <c r="J284" s="4"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A285" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C285" s="8">
         <v>1317346</v>
@@ -9458,12 +9458,12 @@
       <c r="I285" s="4"/>
       <c r="J285" s="4"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C286" s="14">
         <v>201</v>
@@ -9478,15 +9478,15 @@
       <c r="I286" s="4"/>
       <c r="J286" s="4"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B287" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="B287" s="4" t="s">
-        <v>344</v>
-      </c>
       <c r="C287" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4">
@@ -9498,12 +9498,12 @@
       <c r="I287" s="4"/>
       <c r="J287" s="4"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C288" s="5">
         <v>7487947</v>
@@ -9520,15 +9520,15 @@
       <c r="I288" s="4"/>
       <c r="J288" s="4"/>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="4">
@@ -9540,15 +9540,15 @@
       <c r="I289" s="4"/>
       <c r="J289" s="4"/>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D290" s="4"/>
       <c r="E290" s="4">
@@ -9560,12 +9560,12 @@
       <c r="I290" s="4"/>
       <c r="J290" s="4"/>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C291" s="5">
         <v>7439976</v>
@@ -9588,12 +9588,12 @@
         <v>5.9999999999999995E-4</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C292" s="5">
         <v>22967926</v>
@@ -9608,15 +9608,15 @@
       <c r="I292" s="4"/>
       <c r="J292" s="4"/>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D293" s="4">
         <v>0</v>
@@ -9630,15 +9630,15 @@
       <c r="I293" s="4"/>
       <c r="J293" s="4"/>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D294" s="4"/>
       <c r="E294" s="4">
@@ -9650,12 +9650,12 @@
       <c r="I294" s="4"/>
       <c r="J294" s="4"/>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C295" s="5">
         <v>22967926</v>
@@ -9672,15 +9672,15 @@
       <c r="I295" s="4"/>
       <c r="J295" s="4"/>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D296" s="4"/>
       <c r="E296" s="4">
@@ -9692,12 +9692,12 @@
       <c r="I296" s="4"/>
       <c r="J296" s="4"/>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C297" s="14">
         <v>202</v>
@@ -9712,12 +9712,12 @@
       <c r="I297" s="4"/>
       <c r="J297" s="4"/>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C298" s="5">
         <v>62384</v>
@@ -9734,12 +9734,12 @@
       <c r="I298" s="4"/>
       <c r="J298" s="4"/>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C299" s="5">
         <v>67561</v>
@@ -9766,12 +9766,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C300" s="5">
         <v>72435</v>
@@ -9786,12 +9786,12 @@
       <c r="I300" s="4"/>
       <c r="J300" s="4"/>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C301" s="5">
         <v>74839</v>
@@ -9814,12 +9814,12 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C302" s="5">
         <v>74873</v>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="J302" s="4"/>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C303" s="5">
         <v>60344</v>
@@ -9866,12 +9866,12 @@
       <c r="I303" s="4"/>
       <c r="J303" s="4"/>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C304" s="5">
         <v>74884</v>
@@ -9896,12 +9896,12 @@
       </c>
       <c r="J304" s="4"/>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C305" s="5">
         <v>108101</v>
@@ -9918,12 +9918,12 @@
       <c r="I305" s="4"/>
       <c r="J305" s="4"/>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C306" s="5">
         <v>624839</v>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="J306" s="4"/>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C307" s="5">
         <v>80626</v>
@@ -9972,12 +9972,12 @@
       <c r="I307" s="4"/>
       <c r="J307" s="4"/>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C308" s="5">
         <v>1634044</v>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="J308" s="4"/>
     </row>
-    <row r="309" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C309" s="5">
         <v>75092</v>
@@ -10034,12 +10034,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A310" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C310" s="5">
         <v>121697</v>
@@ -10056,12 +10056,12 @@
       <c r="I310" s="4"/>
       <c r="J310" s="4"/>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C311" s="5">
         <v>91203</v>
@@ -10078,12 +10078,12 @@
       <c r="I311" s="4"/>
       <c r="J311" s="4"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A312" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C312" s="8">
         <v>10101970</v>
@@ -10100,12 +10100,12 @@
       <c r="I312" s="4"/>
       <c r="J312" s="37"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A313" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B313" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="B313" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="C313" s="8">
         <v>373024</v>
@@ -10122,12 +10122,12 @@
       <c r="I313" s="4"/>
       <c r="J313" s="37"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A314" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C314" s="5">
         <v>13463393</v>
@@ -10146,12 +10146,12 @@
       <c r="I314" s="4"/>
       <c r="J314" s="37"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A315" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C315" s="5">
         <v>7718549</v>
@@ -10168,12 +10168,12 @@
       <c r="I315" s="4"/>
       <c r="J315" s="37"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C316" s="5">
         <v>7440020</v>
@@ -10190,12 +10190,12 @@
       <c r="I316" s="4"/>
       <c r="J316" s="37"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C317" s="5">
         <v>13138459</v>
@@ -10212,12 +10212,12 @@
       <c r="I317" s="4"/>
       <c r="J317" s="37"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C318" s="5">
         <v>1313991</v>
@@ -10234,15 +10234,15 @@
       <c r="I318" s="4"/>
       <c r="J318" s="37"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D319" s="4">
         <v>2.4000000000000001E-4</v>
@@ -10254,12 +10254,12 @@
       <c r="I319" s="4"/>
       <c r="J319" s="37"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C320" s="5">
         <v>12035722</v>
@@ -10276,12 +10276,12 @@
       <c r="I320" s="4"/>
       <c r="J320" s="37"/>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C321" s="5">
         <v>13770893</v>
@@ -10298,12 +10298,12 @@
       <c r="I321" s="4"/>
       <c r="J321" s="37"/>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C322" s="5">
         <v>7786814</v>
@@ -10320,12 +10320,12 @@
       <c r="I322" s="4"/>
       <c r="J322" s="37"/>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C323" s="5">
         <v>98953</v>
@@ -10342,12 +10342,12 @@
       <c r="I323" s="4"/>
       <c r="J323" s="4"/>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C324" s="5">
         <v>62759</v>
@@ -10364,12 +10364,12 @@
       <c r="I324" s="4"/>
       <c r="J324" s="4"/>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C325" s="5">
         <v>59892</v>
@@ -10386,15 +10386,15 @@
       <c r="I325" s="4"/>
       <c r="J325" s="4"/>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
@@ -10404,12 +10404,12 @@
       <c r="I326" s="4"/>
       <c r="J326" s="4"/>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C327" s="5">
         <v>95534</v>
@@ -10426,12 +10426,12 @@
       <c r="I327" s="4"/>
       <c r="J327" s="4"/>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A328" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C328" s="5">
         <v>56382</v>
@@ -10450,12 +10450,12 @@
       <c r="I328" s="4"/>
       <c r="J328" s="4"/>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A329" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C329" s="5">
         <v>82688</v>
@@ -10470,12 +10470,12 @@
       <c r="I329" s="4"/>
       <c r="J329" s="4"/>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C330" s="5">
         <v>87865</v>
@@ -10490,12 +10490,12 @@
       <c r="I330" s="4"/>
       <c r="J330" s="4"/>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C331" s="5">
         <v>108952</v>
@@ -10522,12 +10522,12 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C332" s="5">
         <v>75445</v>
@@ -10550,12 +10550,12 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C333" s="5">
         <v>7803512</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="J333" s="4"/>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C334" s="5">
         <v>7723140</v>
@@ -10600,12 +10600,12 @@
       <c r="I334" s="4"/>
       <c r="J334" s="4"/>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C335" s="5">
         <v>85449</v>
@@ -10622,15 +10622,15 @@
       <c r="I335" s="4"/>
       <c r="J335" s="4"/>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
@@ -10640,12 +10640,12 @@
       <c r="I336" s="4"/>
       <c r="J336" s="4"/>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C337" s="5">
         <v>12674112</v>
@@ -10662,15 +10662,15 @@
       <c r="I337" s="4"/>
       <c r="J337" s="4"/>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B338" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="B338" s="4" t="s">
-        <v>405</v>
-      </c>
       <c r="C338" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D338" s="4">
         <v>1E-4</v>
@@ -10682,15 +10682,15 @@
       <c r="I338" s="4"/>
       <c r="J338" s="4"/>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D339" s="4">
         <v>1E-4</v>
@@ -10702,15 +10702,15 @@
       <c r="I339" s="4"/>
       <c r="J339" s="4"/>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D340" s="4">
         <v>1E-4</v>
@@ -10722,12 +10722,12 @@
       <c r="I340" s="4"/>
       <c r="J340" s="4"/>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C341" s="5">
         <v>11097691</v>
@@ -10744,15 +10744,15 @@
       <c r="I341" s="4"/>
       <c r="J341" s="4"/>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D342" s="4">
         <v>1E-4</v>
@@ -10764,12 +10764,12 @@
       <c r="I342" s="4"/>
       <c r="J342" s="4"/>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C343" s="5">
         <v>1336363</v>
@@ -10786,15 +10786,15 @@
       <c r="I343" s="4"/>
       <c r="J343" s="4"/>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A344" s="6" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D344" s="4">
         <v>1E-4</v>
@@ -10806,12 +10806,12 @@
       <c r="I344" s="4"/>
       <c r="J344" s="4"/>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A345" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C345" s="5">
         <v>7012375</v>
@@ -10826,12 +10826,12 @@
       <c r="I345" s="4"/>
       <c r="J345" s="4"/>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A346" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C346" s="5">
         <v>2050682</v>
@@ -10846,12 +10846,12 @@
       <c r="I346" s="4"/>
       <c r="J346" s="4"/>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A347" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C347" s="5">
         <v>2051243</v>
@@ -10866,12 +10866,12 @@
       <c r="I347" s="4"/>
       <c r="J347" s="4"/>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A348" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C348" s="5">
         <v>28655712</v>
@@ -10886,12 +10886,12 @@
       <c r="I348" s="4"/>
       <c r="J348" s="4"/>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A349" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C349" s="5">
         <v>26601649</v>
@@ -10906,12 +10906,12 @@
       <c r="I349" s="4"/>
       <c r="J349" s="4"/>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A350" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C350" s="20">
         <v>25429292</v>
@@ -10926,12 +10926,12 @@
       <c r="I350" s="4"/>
       <c r="J350" s="4"/>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A351" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C351" s="5">
         <v>26914330</v>
@@ -10946,12 +10946,12 @@
       <c r="I351" s="4"/>
       <c r="J351" s="4"/>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A352" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C352" s="5"/>
       <c r="D352" s="31">
@@ -10964,12 +10964,12 @@
       <c r="I352" s="4"/>
       <c r="J352" s="4"/>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A353" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C353" s="38">
         <v>40</v>
@@ -10984,15 +10984,15 @@
       <c r="I353" s="4"/>
       <c r="J353" s="4"/>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A354" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C354" s="38" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D354" s="31">
         <v>5.079E-5</v>
@@ -11004,12 +11004,12 @@
       <c r="I354" s="4"/>
       <c r="J354" s="4"/>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A355" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B355" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="B355" s="4" t="s">
-        <v>428</v>
       </c>
       <c r="C355" s="38">
         <v>246</v>
@@ -11024,12 +11024,12 @@
       <c r="I355" s="4"/>
       <c r="J355" s="4"/>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A356" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C356" s="5"/>
       <c r="D356" s="31">
@@ -11042,12 +11042,12 @@
       <c r="I356" s="4"/>
       <c r="J356" s="4"/>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A357" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C357" s="5">
         <v>90120</v>
@@ -11064,12 +11064,12 @@
       <c r="I357" s="4"/>
       <c r="J357" s="4"/>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A358" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B358" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="B358" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="C358" s="5">
         <v>832699</v>
@@ -11084,15 +11084,15 @@
       <c r="I358" s="4"/>
       <c r="J358" s="4"/>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A359" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C359" s="39" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D359" s="31">
         <v>5.079E-5</v>
@@ -11104,12 +11104,12 @@
       <c r="I359" s="4"/>
       <c r="J359" s="4"/>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A360" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C360" s="5">
         <v>2381217</v>
@@ -11124,12 +11124,12 @@
       <c r="I360" s="4"/>
       <c r="J360" s="4"/>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A361" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C361" s="5">
         <v>91576</v>
@@ -11146,15 +11146,15 @@
       <c r="I361" s="4"/>
       <c r="J361" s="4"/>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A362" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C362" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D362" s="31">
         <v>5.079E-5</v>
@@ -11166,12 +11166,12 @@
       <c r="I362" s="4"/>
       <c r="J362" s="4"/>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A363" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C363" s="12">
         <v>2422799</v>
@@ -11186,12 +11186,12 @@
       <c r="I363" s="4"/>
       <c r="J363" s="4"/>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A364" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C364" s="5">
         <v>91587</v>
@@ -11208,12 +11208,12 @@
       <c r="I364" s="4"/>
       <c r="J364" s="4"/>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A365" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C365" s="5">
         <v>83329</v>
@@ -11230,12 +11230,12 @@
       <c r="I365" s="4"/>
       <c r="J365" s="4"/>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A366" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B366" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="B366" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="C366" s="5">
         <v>208968</v>
@@ -11252,12 +11252,12 @@
       <c r="I366" s="4"/>
       <c r="J366" s="4"/>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A367" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C367" s="5">
         <v>120127</v>
@@ -11272,12 +11272,12 @@
       <c r="I367" s="4"/>
       <c r="J367" s="4"/>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A368" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C368" s="5">
         <v>203338</v>
@@ -11292,15 +11292,15 @@
       <c r="I368" s="4"/>
       <c r="J368" s="4"/>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A369" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C369" s="38" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D369" s="31">
         <v>5.079E-5</v>
@@ -11312,12 +11312,12 @@
       <c r="I369" s="4"/>
       <c r="J369" s="4"/>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A370" s="7" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C370" s="8">
         <v>195197</v>
@@ -11332,12 +11332,12 @@
       <c r="I370" s="4"/>
       <c r="J370" s="4"/>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A371" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C371" s="5">
         <v>192972</v>
@@ -11354,12 +11354,12 @@
       <c r="I371" s="4"/>
       <c r="J371" s="4"/>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A372" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C372" s="5">
         <v>56832736</v>
@@ -11374,12 +11374,12 @@
       <c r="I372" s="4"/>
       <c r="J372" s="4"/>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A373" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C373" s="5">
         <v>191242</v>
@@ -11396,15 +11396,15 @@
       <c r="I373" s="4"/>
       <c r="J373" s="4"/>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A374" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D374" s="31">
         <v>5.079E-5</v>
@@ -11416,12 +11416,12 @@
       <c r="I374" s="4"/>
       <c r="J374" s="4"/>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A375" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C375" s="38">
         <v>284</v>
@@ -11436,12 +11436,12 @@
       <c r="I375" s="4"/>
       <c r="J375" s="4"/>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A376" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C376" s="5">
         <v>206440</v>
@@ -11458,12 +11458,12 @@
       <c r="I376" s="4"/>
       <c r="J376" s="4"/>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A377" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C377" s="5">
         <v>86737</v>
@@ -11480,15 +11480,15 @@
       <c r="I377" s="4"/>
       <c r="J377" s="4"/>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A378" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D378" s="31">
         <v>5.079E-5</v>
@@ -11500,12 +11500,12 @@
       <c r="I378" s="4"/>
       <c r="J378" s="4"/>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A379" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C379" s="5">
         <v>26914181</v>
@@ -11520,15 +11520,15 @@
       <c r="I379" s="4"/>
       <c r="J379" s="4"/>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A380" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D380" s="31">
         <v>5.079E-5</v>
@@ -11540,12 +11540,12 @@
       <c r="I380" s="4"/>
       <c r="J380" s="4"/>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A381" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C381" s="5">
         <v>65357699</v>
@@ -11560,15 +11560,15 @@
       <c r="I381" s="4"/>
       <c r="J381" s="4"/>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A382" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D382" s="31">
         <v>5.079E-5</v>
@@ -11580,12 +11580,12 @@
       <c r="I382" s="4"/>
       <c r="J382" s="4"/>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A383" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C383" s="8">
         <v>198550</v>
@@ -11600,12 +11600,12 @@
       <c r="I383" s="4"/>
       <c r="J383" s="4"/>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A384" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C384" s="5">
         <v>85018</v>
@@ -11620,12 +11620,12 @@
       <c r="I384" s="4"/>
       <c r="J384" s="4"/>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A385" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C385" s="5">
         <v>129000</v>
@@ -11640,12 +11640,12 @@
       <c r="I385" s="4"/>
       <c r="J385" s="4"/>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A386" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C386" s="5"/>
       <c r="D386" s="31">
@@ -11658,12 +11658,12 @@
       <c r="I386" s="4"/>
       <c r="J386" s="4"/>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A387" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C387" s="5">
         <v>57976</v>
@@ -11680,12 +11680,12 @@
       <c r="I387" s="4"/>
       <c r="J387" s="4"/>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A388" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C388" s="5"/>
       <c r="D388" s="31">
@@ -11698,12 +11698,12 @@
       <c r="I388" s="4"/>
       <c r="J388" s="4"/>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A389" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C389" s="5">
         <v>42397648</v>
@@ -11720,12 +11720,12 @@
       <c r="I389" s="4"/>
       <c r="J389" s="4"/>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A390" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B390" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="B390" s="4" t="s">
-        <v>473</v>
       </c>
       <c r="C390" s="5">
         <v>56495</v>
@@ -11742,12 +11742,12 @@
       <c r="I390" s="4"/>
       <c r="J390" s="4"/>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A391" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C391" s="5">
         <v>7496028</v>
@@ -11764,12 +11764,12 @@
       <c r="I391" s="4"/>
       <c r="J391" s="4"/>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A392" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C392" s="5">
         <v>189640</v>
@@ -11786,12 +11786,12 @@
       <c r="I392" s="4"/>
       <c r="J392" s="4"/>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A393" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C393" s="5">
         <v>189559</v>
@@ -11808,12 +11808,12 @@
       <c r="I393" s="4"/>
       <c r="J393" s="4"/>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A394" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C394" s="5">
         <v>191300</v>
@@ -11830,12 +11830,12 @@
       <c r="I394" s="4"/>
       <c r="J394" s="4"/>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A395" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C395" s="5"/>
       <c r="D395" s="31">
@@ -11848,12 +11848,12 @@
       <c r="I395" s="4"/>
       <c r="J395" s="4"/>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A396" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C396" s="5">
         <v>42397659</v>
@@ -11870,15 +11870,15 @@
       <c r="I396" s="4"/>
       <c r="J396" s="4"/>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A397" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B397" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="B397" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="C397" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D397" s="4">
         <v>2.1540000000000001E-3</v>
@@ -11890,15 +11890,15 @@
       <c r="I397" s="4"/>
       <c r="J397" s="4"/>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A398" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D398" s="31">
         <v>1.016E-3</v>
@@ -11910,12 +11910,12 @@
       <c r="I398" s="4"/>
       <c r="J398" s="4"/>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A399" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C399" s="5">
         <v>3697243</v>
@@ -11932,12 +11932,12 @@
       <c r="I399" s="4"/>
       <c r="J399" s="4"/>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A400" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C400" s="5">
         <v>194592</v>
@@ -11954,12 +11954,12 @@
       <c r="I400" s="4"/>
       <c r="J400" s="4"/>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A401" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C401" s="5">
         <v>50328</v>
@@ -11976,12 +11976,12 @@
       <c r="I401" s="4"/>
       <c r="J401" s="4"/>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A402" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C402" s="5">
         <v>192654</v>
@@ -11998,12 +11998,12 @@
       <c r="I402" s="4"/>
       <c r="J402" s="4"/>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A403" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C403" s="5">
         <v>53703</v>
@@ -12020,15 +12020,15 @@
       <c r="I403" s="4"/>
       <c r="J403" s="4"/>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A404" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D404" s="31">
         <v>1.016E-3</v>
@@ -12042,12 +12042,12 @@
       <c r="I404" s="4"/>
       <c r="J404" s="4"/>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A405" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C405" s="5"/>
       <c r="D405" s="31">
@@ -12060,12 +12060,12 @@
       <c r="I405" s="4"/>
       <c r="J405" s="4"/>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A406" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C406" s="5">
         <v>5522430</v>
@@ -12082,12 +12082,12 @@
       <c r="I406" s="4"/>
       <c r="J406" s="4"/>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A407" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B407" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="B407" s="4" t="s">
-        <v>496</v>
       </c>
       <c r="C407" s="5">
         <v>57835924</v>
@@ -12104,12 +12104,12 @@
       <c r="I407" s="4"/>
       <c r="J407" s="4"/>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A408" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C408" s="5">
         <v>602879</v>
@@ -12126,12 +12126,12 @@
       <c r="I408" s="4"/>
       <c r="J408" s="4"/>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A409" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C409" s="5">
         <v>56553</v>
@@ -12148,12 +12148,12 @@
       <c r="I409" s="4"/>
       <c r="J409" s="4"/>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A410" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B410" s="4" t="s">
         <v>501</v>
-      </c>
-      <c r="B410" s="4" t="s">
-        <v>500</v>
       </c>
       <c r="C410" s="5">
         <v>205992</v>
@@ -12170,12 +12170,12 @@
       <c r="I410" s="4"/>
       <c r="J410" s="4"/>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A411" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C411" s="38">
         <v>102</v>
@@ -12190,12 +12190,12 @@
       <c r="I411" s="4"/>
       <c r="J411" s="4"/>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A412" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C412" s="5">
         <v>205823</v>
@@ -12212,12 +12212,12 @@
       <c r="I412" s="4"/>
       <c r="J412" s="4"/>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A413" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C413" s="5">
         <v>226368</v>
@@ -12234,12 +12234,12 @@
       <c r="I413" s="4"/>
       <c r="J413" s="4"/>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A414" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C414" s="5">
         <v>224420</v>
@@ -12256,12 +12256,12 @@
       <c r="I414" s="4"/>
       <c r="J414" s="4"/>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A415" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C415" s="5">
         <v>193395</v>
@@ -12278,12 +12278,12 @@
       <c r="I415" s="4"/>
       <c r="J415" s="4"/>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A416" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C416" s="5"/>
       <c r="D416" s="31">
@@ -12296,12 +12296,12 @@
       <c r="I416" s="4"/>
       <c r="J416" s="4"/>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A417" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C417" s="5">
         <v>207089</v>
@@ -12318,15 +12318,15 @@
       <c r="I417" s="4"/>
       <c r="J417" s="4"/>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A418" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D418" s="34">
         <v>1.558E-5</v>
@@ -12338,12 +12338,12 @@
       <c r="I418" s="4"/>
       <c r="J418" s="4"/>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A419" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C419" s="5">
         <v>607578</v>
@@ -12360,12 +12360,12 @@
       <c r="I419" s="4"/>
       <c r="J419" s="4"/>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A420" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C420" s="5">
         <v>86748</v>
@@ -12382,18 +12382,18 @@
       <c r="I420" s="4"/>
       <c r="J420" s="4"/>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A421" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C421" s="5">
         <v>218019</v>
       </c>
       <c r="D421" s="40" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E421" s="4">
         <v>0</v>
@@ -12404,12 +12404,12 @@
       <c r="I421" s="4"/>
       <c r="J421" s="4"/>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A422" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C422" s="5"/>
       <c r="D422" s="31">
@@ -12422,12 +12422,12 @@
       <c r="I422" s="4"/>
       <c r="J422" s="4"/>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A423" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C423" s="14">
         <v>75</v>
@@ -12442,12 +12442,12 @@
       <c r="I423" s="4"/>
       <c r="J423" s="4"/>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A424" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C424" s="5">
         <v>106503</v>
@@ -12464,12 +12464,12 @@
       <c r="I424" s="4"/>
       <c r="J424" s="4"/>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A425" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C425" s="5">
         <v>123386</v>
@@ -12490,12 +12490,12 @@
       <c r="I425" s="4"/>
       <c r="J425" s="4"/>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A426" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C426" s="5">
         <v>114261</v>
@@ -12512,12 +12512,12 @@
       <c r="I426" s="4"/>
       <c r="J426" s="4"/>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A427" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C427" s="5">
         <v>78875</v>
@@ -12532,12 +12532,12 @@
       <c r="I427" s="4"/>
       <c r="J427" s="4"/>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A428" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C428" s="5">
         <v>75569</v>
@@ -12564,12 +12564,12 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A429" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C429" s="5">
         <v>91225</v>
@@ -12586,12 +12586,12 @@
       <c r="I429" s="4"/>
       <c r="J429" s="4"/>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A430" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C430" s="5">
         <v>106514</v>
@@ -12608,12 +12608,12 @@
       <c r="I430" s="4"/>
       <c r="J430" s="4"/>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A431" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C431" s="38">
         <v>605</v>
@@ -12626,15 +12626,15 @@
       <c r="I431" s="4"/>
       <c r="J431" s="4"/>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A432" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="B432" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="B432" s="4" t="s">
-        <v>530</v>
-      </c>
       <c r="C432" s="39" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -12644,15 +12644,15 @@
       <c r="I432" s="4"/>
       <c r="J432" s="4"/>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A433" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C433" s="38" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -12662,12 +12662,12 @@
       <c r="I433" s="4"/>
       <c r="J433" s="4"/>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A434" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C434" s="38"/>
       <c r="D434" s="4"/>
@@ -12678,12 +12678,12 @@
       <c r="I434" s="4"/>
       <c r="J434" s="4"/>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A435" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C435" s="38"/>
       <c r="D435" s="4"/>
@@ -12694,12 +12694,12 @@
       <c r="I435" s="4"/>
       <c r="J435" s="4"/>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A436" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C436" s="8">
         <v>7440611</v>
@@ -12714,15 +12714,15 @@
       <c r="I436" s="4"/>
       <c r="J436" s="4"/>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A437" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="J437" s="4"/>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A438" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C438" s="5">
         <v>7440611</v>
@@ -12758,12 +12758,12 @@
       <c r="I438" s="4"/>
       <c r="J438" s="4"/>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A439" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C439" s="5">
         <v>7783815</v>
@@ -12788,15 +12788,15 @@
       </c>
       <c r="J439" s="4"/>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A440" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4">
@@ -12810,15 +12810,15 @@
       </c>
       <c r="J440" s="4"/>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A441" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D441" s="4">
         <v>0</v>
@@ -12832,15 +12832,15 @@
       <c r="I441" s="4"/>
       <c r="J441" s="4"/>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A442" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4">
@@ -12852,15 +12852,15 @@
       <c r="I442" s="4"/>
       <c r="J442" s="4"/>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A443" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4">
@@ -12872,12 +12872,12 @@
       <c r="I443" s="4"/>
       <c r="J443" s="4"/>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A444" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C444" s="5">
         <v>7783075</v>
@@ -12898,15 +12898,15 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A445" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="B445" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="B445" s="4" t="s">
-        <v>551</v>
-      </c>
       <c r="C445" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D445" s="35"/>
       <c r="E445" s="4">
@@ -12918,12 +12918,12 @@
       <c r="I445" s="4"/>
       <c r="J445" s="4"/>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A446" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C446" s="5">
         <v>7783008</v>
@@ -12940,12 +12940,12 @@
       <c r="I446" s="4"/>
       <c r="J446" s="4"/>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A447" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C447" s="5">
         <v>7782492</v>
@@ -12962,12 +12962,12 @@
       <c r="I447" s="4"/>
       <c r="J447" s="4"/>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A448" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C448" s="5">
         <v>7446084</v>
@@ -12982,15 +12982,15 @@
       <c r="I448" s="4"/>
       <c r="J448" s="4"/>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A449" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4">
@@ -13002,12 +13002,12 @@
       <c r="I449" s="4"/>
       <c r="J449" s="4"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A450" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C450" s="5">
         <v>7783791</v>
@@ -13026,12 +13026,12 @@
       <c r="I450" s="4"/>
       <c r="J450" s="4"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A451" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C451" s="5">
         <v>12640890</v>
@@ -13046,15 +13046,15 @@
       <c r="I451" s="4"/>
       <c r="J451" s="4"/>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A452" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4">
@@ -13066,15 +13066,15 @@
       <c r="I452" s="4"/>
       <c r="J452" s="4"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A453" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4">
@@ -13086,12 +13086,12 @@
       <c r="I453" s="4"/>
       <c r="J453" s="4"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A454" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C454" s="5">
         <v>630104</v>
@@ -13108,15 +13108,15 @@
       <c r="I454" s="4"/>
       <c r="J454" s="4"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A455" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C455" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4">
@@ -13128,15 +13128,15 @@
       <c r="I455" s="4"/>
       <c r="J455" s="4"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A456" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C456" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4">
@@ -13148,12 +13148,12 @@
       <c r="I456" s="4"/>
       <c r="J456" s="4"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A457" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C457" s="5">
         <v>100425</v>
@@ -13180,12 +13180,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A458" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C458" s="5">
         <v>96093</v>
@@ -13200,12 +13200,12 @@
       <c r="I458" s="4"/>
       <c r="J458" s="4"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A459" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C459" s="5">
         <v>127184</v>
@@ -13232,12 +13232,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A460" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C460" s="5">
         <v>7550450</v>
@@ -13260,12 +13260,12 @@
       </c>
       <c r="J460" s="4"/>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A461" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C461" s="5">
         <v>108883</v>
@@ -13290,12 +13290,12 @@
       </c>
       <c r="J461" s="4"/>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A462" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C462" s="5">
         <v>8001352</v>
@@ -13312,12 +13312,12 @@
       <c r="I462" s="4"/>
       <c r="J462" s="4"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A463" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C463" s="5">
         <v>79016</v>
@@ -13342,12 +13342,12 @@
       </c>
       <c r="J463" s="4"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A464" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C464" s="5">
         <v>121448</v>
@@ -13366,12 +13366,12 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A465" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C465" s="5">
         <v>1582098</v>
@@ -13386,12 +13386,12 @@
       <c r="I465" s="4"/>
       <c r="J465" s="4"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A466" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C466" s="5">
         <v>108054</v>
@@ -13416,12 +13416,12 @@
       </c>
       <c r="J466" s="4"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A467" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C467" s="5">
         <v>593602</v>
@@ -13438,12 +13438,12 @@
       <c r="I467" s="4"/>
       <c r="J467" s="4"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A468" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C468" s="5">
         <v>75014</v>
@@ -13470,12 +13470,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A469" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C469" s="5">
         <v>75354</v>
@@ -13494,12 +13494,12 @@
       </c>
       <c r="J469" s="4"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A470" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C470" s="5">
         <v>108383</v>
@@ -13518,12 +13518,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A471" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B471" s="4" t="s">
         <v>584</v>
-      </c>
-      <c r="B471" s="4" t="s">
-        <v>583</v>
       </c>
       <c r="C471" s="5">
         <v>95476</v>
@@ -13542,12 +13542,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A472" s="21" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B472" s="21" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C472" s="20">
         <v>106423</v>
@@ -13566,12 +13566,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A473" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C473" s="5">
         <v>1330207</v>
@@ -13594,15 +13594,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A474" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D474" s="4"/>
       <c r="E474" s="4"/>
@@ -13612,12 +13612,12 @@
       <c r="I474" s="24"/>
       <c r="J474" s="23"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A475" s="18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C475" s="12">
         <v>67425</v>
@@ -13632,15 +13632,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A476" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C476" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D476" s="4"/>
       <c r="E476" s="4"/>
@@ -13650,12 +13650,12 @@
       <c r="I476" s="4"/>
       <c r="J476" s="4"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A477" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C477" s="5">
         <v>1589497</v>
@@ -13668,12 +13668,12 @@
       <c r="I477" s="4"/>
       <c r="J477" s="4"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A478" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C478" s="5">
         <v>16672392</v>
@@ -13686,12 +13686,12 @@
       <c r="I478" s="4"/>
       <c r="J478" s="4"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A479" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C479" s="8">
         <v>120558</v>
@@ -13704,15 +13704,15 @@
       <c r="I479" s="4"/>
       <c r="J479" s="4"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A480" s="18" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C480" s="19" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D480" s="4"/>
       <c r="E480" s="4"/>
@@ -13722,15 +13722,15 @@
       <c r="I480" s="4"/>
       <c r="J480" s="4"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A481" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D481" s="4"/>
       <c r="E481" s="4"/>
@@ -13740,9 +13740,9 @@
       <c r="I481" s="4"/>
       <c r="J481" s="4"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A482" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B482" s="4"/>
       <c r="C482" s="5"/>
@@ -13754,9 +13754,9 @@
       <c r="I482" s="25"/>
       <c r="J482" s="25"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A483" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B483" s="4"/>
       <c r="C483" s="5"/>
@@ -13768,9 +13768,9 @@
       <c r="I483" s="25"/>
       <c r="J483" s="25"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A484" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B484" s="4"/>
       <c r="C484" s="5"/>
@@ -13782,9 +13782,9 @@
       <c r="I484" s="25"/>
       <c r="J484" s="25"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A485" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B485" s="4"/>
       <c r="C485" s="5"/>
@@ -13796,9 +13796,9 @@
       <c r="I485" s="25"/>
       <c r="J485" s="25"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A486" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B486" s="4"/>
       <c r="C486" s="5"/>
@@ -13810,9 +13810,9 @@
       <c r="I486" s="25"/>
       <c r="J486" s="25"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A487" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B487" s="4"/>
       <c r="C487" s="5"/>
@@ -13824,9 +13824,9 @@
       <c r="I487" s="25"/>
       <c r="J487" s="25"/>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A488" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B488" s="4"/>
       <c r="C488" s="5"/>
@@ -13838,9 +13838,9 @@
       <c r="I488" s="25"/>
       <c r="J488" s="25"/>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A489" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B489" s="4"/>
       <c r="C489" s="5"/>
@@ -13852,9 +13852,9 @@
       <c r="I489" s="25"/>
       <c r="J489" s="25"/>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A490" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B490" s="4"/>
       <c r="C490" s="5"/>
@@ -13866,9 +13866,9 @@
       <c r="I490" s="25"/>
       <c r="J490" s="25"/>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A491" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B491" s="4"/>
       <c r="C491" s="5"/>
@@ -13880,9 +13880,9 @@
       <c r="I491" s="25"/>
       <c r="J491" s="25"/>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A492" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B492" s="4"/>
       <c r="C492" s="5"/>
@@ -13894,9 +13894,9 @@
       <c r="I492" s="25"/>
       <c r="J492" s="25"/>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A493" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B493" s="4"/>
       <c r="C493" s="5"/>
@@ -13908,9 +13908,9 @@
       <c r="I493" s="25"/>
       <c r="J493" s="25"/>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A494" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B494" s="4"/>
       <c r="C494" s="5"/>
@@ -13922,9 +13922,9 @@
       <c r="I494" s="25"/>
       <c r="J494" s="25"/>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A495" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B495" s="4"/>
       <c r="C495" s="5"/>
@@ -13936,9 +13936,9 @@
       <c r="I495" s="25"/>
       <c r="J495" s="25"/>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A496" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B496" s="4"/>
       <c r="C496" s="5"/>
@@ -13950,9 +13950,9 @@
       <c r="I496" s="25"/>
       <c r="J496" s="25"/>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A497" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B497" s="4"/>
       <c r="C497" s="5"/>
@@ -13964,9 +13964,9 @@
       <c r="I497" s="25"/>
       <c r="J497" s="25"/>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A498" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B498" s="4"/>
       <c r="D498" s="4"/>
@@ -13977,9 +13977,9 @@
       <c r="I498" s="25"/>
       <c r="J498" s="25"/>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A499" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B499" s="4"/>
       <c r="C499" s="5"/>
@@ -13997,7 +13997,7 @@
   <pageMargins left="0.17" right="0.17" top="0.47" bottom="0.57999999999999996" header="0" footer="0"/>
   <pageSetup paperSize="5" scale="89" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;F&amp;C&amp;P&amp;RNovember 15, 2024</oddFooter>
+    <oddFooter>&amp;L&amp;F&amp;C&amp;P&amp;RMay 6, 2025</oddFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/resources/Dose_Response_Library.xlsx
+++ b/resources/Dose_Response_Library.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scainccloud-my.sharepoint.com/personal/jmozier_scainc_com/Documents/Projects/ASRA-RIS-BasePeriod/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/pfohl_marisa_epa_gov/Documents/Documents/Documents/OAR/Dose-Response Prioritization/OAQPS Toxicity Tables/HEM Dose-Response Library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DF64BD5-AAA7-4B3A-9E76-99ABBD218580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{1E49F806-3F0B-4453-9D02-3968BE15D137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8451EBF1-0B5B-417B-9591-A5F2AD9A4079}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="1500" windowWidth="26700" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dose Response Value Library" sheetId="1" r:id="rId1"/>
@@ -1400,9 +1400,6 @@
     <t>Anthracene</t>
   </si>
   <si>
-    <t>POM as 15-PAH</t>
-  </si>
-  <si>
     <t>Benzo(a)fluoranthene</t>
   </si>
   <si>
@@ -1965,6 +1962,9 @@
   </si>
   <si>
     <t>106-94-5</t>
+  </si>
+  <si>
+    <t>POM 72002; POM as 15-PAH</t>
   </si>
 </sst>
 </file>
@@ -2461,7 +2461,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2537,6 +2537,12 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="47">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -2969,22 +2975,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J499"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" customWidth="1"/>
+    <col min="1" max="1" width="36.7265625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" customWidth="1"/>
     <col min="3" max="3" width="14" style="26" customWidth="1"/>
     <col min="4" max="4" width="21" style="6" customWidth="1"/>
     <col min="5" max="5" width="11" style="6" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="27" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" style="27" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" style="27" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" style="27" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" style="27" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" style="27" customWidth="1"/>
+    <col min="8" max="8" width="9.7265625" style="27" customWidth="1"/>
+    <col min="9" max="9" width="9.26953125" style="27" customWidth="1"/>
     <col min="10" max="10" width="12" style="27" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="6"/>
+    <col min="11" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2998,7 +3004,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -3013,10 +3019,10 @@
         <v>7</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -3048,7 +3054,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -3068,7 +3074,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -3088,7 +3094,7 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -3112,7 +3118,7 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -3132,7 +3138,7 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
@@ -3152,7 +3158,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -3172,7 +3178,7 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -3194,7 +3200,7 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -3216,7 +3222,7 @@
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
@@ -3238,7 +3244,7 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
@@ -3260,7 +3266,7 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -3286,7 +3292,7 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -3310,7 +3316,7 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -3340,7 +3346,7 @@
       </c>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -3362,7 +3368,7 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -3384,7 +3390,7 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
@@ -3398,15 +3404,17 @@
         <v>1.1E-5</v>
       </c>
       <c r="E18" s="4">
-        <v>0.06</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J18" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
@@ -3428,7 +3436,7 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
@@ -3456,15 +3464,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>629</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>630</v>
       </c>
       <c r="D21" s="4">
         <v>9.9999999999999995E-7</v>
@@ -3476,7 +3484,7 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>31</v>
       </c>
@@ -3494,7 +3502,7 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>32</v>
       </c>
@@ -3516,7 +3524,7 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
@@ -3538,7 +3546,7 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>34</v>
       </c>
@@ -3560,7 +3568,7 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>36</v>
       </c>
@@ -3582,7 +3590,7 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>37</v>
       </c>
@@ -3602,7 +3610,7 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>38</v>
       </c>
@@ -3622,7 +3630,7 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>39</v>
       </c>
@@ -3644,7 +3652,7 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>40</v>
       </c>
@@ -3676,7 +3684,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>41</v>
       </c>
@@ -3708,7 +3716,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>42</v>
       </c>
@@ -3728,7 +3736,7 @@
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>43</v>
       </c>
@@ -3750,7 +3758,7 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>44</v>
       </c>
@@ -3772,7 +3780,7 @@
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>45</v>
       </c>
@@ -3792,7 +3800,7 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>46</v>
       </c>
@@ -3812,7 +3820,7 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>47</v>
       </c>
@@ -3834,7 +3842,7 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>48</v>
       </c>
@@ -3856,7 +3864,7 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>49</v>
       </c>
@@ -3882,7 +3890,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>51</v>
       </c>
@@ -3904,7 +3912,7 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>53</v>
       </c>
@@ -3922,7 +3930,7 @@
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>54</v>
       </c>
@@ -3940,7 +3948,7 @@
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>55</v>
       </c>
@@ -3962,7 +3970,7 @@
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>56</v>
       </c>
@@ -3994,7 +4002,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>57</v>
       </c>
@@ -4016,7 +4024,7 @@
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>58</v>
       </c>
@@ -4042,7 +4050,7 @@
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>59</v>
       </c>
@@ -4064,7 +4072,7 @@
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>60</v>
       </c>
@@ -4078,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="9">
-        <v>3.5E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="F48" s="9">
         <v>6.9000000000000006E-2</v>
@@ -4096,7 +4104,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>61</v>
       </c>
@@ -4118,7 +4126,7 @@
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>62</v>
       </c>
@@ -4150,7 +4158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>63</v>
       </c>
@@ -4178,7 +4186,7 @@
       </c>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>64</v>
       </c>
@@ -4208,7 +4216,7 @@
       </c>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>65</v>
       </c>
@@ -4234,7 +4242,7 @@
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>66</v>
       </c>
@@ -4256,7 +4264,7 @@
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>67</v>
       </c>
@@ -4278,7 +4286,7 @@
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>68</v>
       </c>
@@ -4298,7 +4306,7 @@
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>69</v>
       </c>
@@ -4318,7 +4326,7 @@
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>71</v>
       </c>
@@ -4340,7 +4348,7 @@
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>72</v>
       </c>
@@ -4362,7 +4370,7 @@
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>73</v>
       </c>
@@ -4384,7 +4392,7 @@
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>74</v>
       </c>
@@ -4408,7 +4416,7 @@
       </c>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>76</v>
       </c>
@@ -4430,7 +4438,7 @@
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>77</v>
       </c>
@@ -4454,7 +4462,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>79</v>
       </c>
@@ -4478,7 +4486,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>80</v>
       </c>
@@ -4502,7 +4510,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
         <v>82</v>
       </c>
@@ -4528,7 +4536,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>84</v>
       </c>
@@ -4552,7 +4560,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>86</v>
       </c>
@@ -4578,7 +4586,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>87</v>
       </c>
@@ -4604,7 +4612,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>88</v>
       </c>
@@ -4634,7 +4642,7 @@
       </c>
       <c r="J70" s="4"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>89</v>
       </c>
@@ -4654,7 +4662,7 @@
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>90</v>
       </c>
@@ -4674,7 +4682,7 @@
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>91</v>
       </c>
@@ -4702,7 +4710,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>92</v>
       </c>
@@ -4724,7 +4732,7 @@
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>93</v>
       </c>
@@ -4748,7 +4756,7 @@
       </c>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>95</v>
       </c>
@@ -4770,7 +4778,7 @@
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>97</v>
       </c>
@@ -4792,7 +4800,7 @@
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>99</v>
       </c>
@@ -4814,7 +4822,7 @@
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>101</v>
       </c>
@@ -4832,7 +4840,7 @@
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>102</v>
       </c>
@@ -4856,7 +4864,7 @@
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>103</v>
       </c>
@@ -4876,7 +4884,7 @@
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>104</v>
       </c>
@@ -4902,7 +4910,7 @@
       </c>
       <c r="J82" s="4"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>105</v>
       </c>
@@ -4924,7 +4932,7 @@
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>106</v>
       </c>
@@ -4946,7 +4954,7 @@
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>107</v>
       </c>
@@ -4972,7 +4980,7 @@
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>108</v>
       </c>
@@ -4994,7 +5002,7 @@
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>110</v>
       </c>
@@ -5016,7 +5024,7 @@
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>111</v>
       </c>
@@ -5038,7 +5046,7 @@
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>112</v>
       </c>
@@ -5060,7 +5068,7 @@
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>114</v>
       </c>
@@ -5080,7 +5088,7 @@
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>115</v>
       </c>
@@ -5102,7 +5110,7 @@
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>116</v>
       </c>
@@ -5134,7 +5142,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>117</v>
       </c>
@@ -5164,7 +5172,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>118</v>
       </c>
@@ -5186,7 +5194,7 @@
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>120</v>
       </c>
@@ -5204,7 +5212,7 @@
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>121</v>
       </c>
@@ -5226,7 +5234,7 @@
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>122</v>
       </c>
@@ -5248,7 +5256,7 @@
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>123</v>
       </c>
@@ -5280,7 +5288,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>124</v>
       </c>
@@ -5304,7 +5312,7 @@
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>125</v>
       </c>
@@ -5330,7 +5338,7 @@
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>126</v>
       </c>
@@ -5352,7 +5360,7 @@
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>127</v>
       </c>
@@ -5380,7 +5388,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>128</v>
       </c>
@@ -5406,7 +5414,7 @@
       </c>
       <c r="J103" s="4"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>129</v>
       </c>
@@ -5428,7 +5436,7 @@
       <c r="I104" s="4"/>
       <c r="J104" s="4"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>130</v>
       </c>
@@ -5450,7 +5458,7 @@
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>132</v>
       </c>
@@ -5472,7 +5480,7 @@
       <c r="I106" s="4"/>
       <c r="J106" s="4"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>133</v>
       </c>
@@ -5494,7 +5502,7 @@
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="18" t="s">
         <v>134</v>
       </c>
@@ -5516,7 +5524,7 @@
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="18" t="s">
         <v>135</v>
       </c>
@@ -5538,7 +5546,7 @@
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>137</v>
       </c>
@@ -5556,7 +5564,7 @@
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>138</v>
       </c>
@@ -5574,7 +5582,7 @@
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>139</v>
       </c>
@@ -5596,7 +5604,7 @@
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>140</v>
       </c>
@@ -5618,7 +5626,7 @@
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>141</v>
       </c>
@@ -5640,7 +5648,7 @@
       <c r="I114" s="4"/>
       <c r="J114" s="4"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="18" t="s">
         <v>142</v>
       </c>
@@ -5662,7 +5670,7 @@
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>143</v>
       </c>
@@ -5684,7 +5692,7 @@
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>144</v>
       </c>
@@ -5706,7 +5714,7 @@
       <c r="I117" s="4"/>
       <c r="J117" s="4"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>145</v>
       </c>
@@ -5724,7 +5732,7 @@
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>131</v>
       </c>
@@ -5746,7 +5754,7 @@
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>147</v>
       </c>
@@ -5768,7 +5776,7 @@
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>148</v>
       </c>
@@ -5786,7 +5794,7 @@
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>149</v>
       </c>
@@ -5808,7 +5816,7 @@
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>150</v>
       </c>
@@ -5830,7 +5838,7 @@
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>151</v>
       </c>
@@ -5852,7 +5860,7 @@
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>152</v>
       </c>
@@ -5874,7 +5882,7 @@
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>153</v>
       </c>
@@ -5896,7 +5904,7 @@
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="18" t="s">
         <v>154</v>
       </c>
@@ -5918,7 +5926,7 @@
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="18" t="s">
         <v>155</v>
       </c>
@@ -5936,7 +5944,7 @@
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>156</v>
       </c>
@@ -5958,7 +5966,7 @@
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>157</v>
       </c>
@@ -5978,7 +5986,7 @@
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>159</v>
       </c>
@@ -5998,7 +6006,7 @@
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>161</v>
       </c>
@@ -6018,7 +6026,7 @@
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>163</v>
       </c>
@@ -6038,7 +6046,7 @@
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>165</v>
       </c>
@@ -6058,7 +6066,7 @@
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>158</v>
       </c>
@@ -6080,7 +6088,7 @@
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>167</v>
       </c>
@@ -6102,7 +6110,7 @@
       </c>
       <c r="J136" s="4"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>169</v>
       </c>
@@ -6122,7 +6130,7 @@
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>170</v>
       </c>
@@ -6142,7 +6150,7 @@
       <c r="I138" s="4"/>
       <c r="J138" s="4"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>172</v>
       </c>
@@ -6162,7 +6170,7 @@
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>173</v>
       </c>
@@ -6182,7 +6190,7 @@
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
     </row>
-    <row r="141" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>174</v>
       </c>
@@ -6202,7 +6210,7 @@
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>175</v>
       </c>
@@ -6222,9 +6230,9 @@
       <c r="I142" s="4"/>
       <c r="J142" s="4"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>176</v>
@@ -6242,7 +6250,7 @@
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>177</v>
       </c>
@@ -6264,7 +6272,7 @@
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>178</v>
       </c>
@@ -6284,7 +6292,7 @@
       <c r="I145" s="4"/>
       <c r="J145" s="4"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>179</v>
       </c>
@@ -6306,7 +6314,7 @@
       <c r="I146" s="4"/>
       <c r="J146" s="4"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>181</v>
       </c>
@@ -6328,7 +6336,7 @@
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>182</v>
       </c>
@@ -6350,7 +6358,7 @@
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>183</v>
       </c>
@@ -6372,7 +6380,7 @@
       <c r="I149" s="4"/>
       <c r="J149" s="4"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>184</v>
       </c>
@@ -6398,7 +6406,7 @@
       <c r="I150" s="4"/>
       <c r="J150" s="4"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>185</v>
       </c>
@@ -6424,7 +6432,7 @@
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>187</v>
       </c>
@@ -6444,7 +6452,7 @@
       <c r="I152" s="4"/>
       <c r="J152" s="4"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>189</v>
       </c>
@@ -6464,7 +6472,7 @@
       <c r="I153" s="4"/>
       <c r="J153" s="4"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>191</v>
       </c>
@@ -6490,7 +6498,7 @@
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>192</v>
       </c>
@@ -6512,7 +6520,7 @@
       <c r="I155" s="4"/>
       <c r="J155" s="4"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>193</v>
       </c>
@@ -6532,7 +6540,7 @@
       <c r="I156" s="4"/>
       <c r="J156" s="4"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>194</v>
       </c>
@@ -6552,7 +6560,7 @@
       <c r="I157" s="4"/>
       <c r="J157" s="4"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>186</v>
       </c>
@@ -6574,7 +6582,7 @@
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>195</v>
       </c>
@@ -6600,7 +6608,7 @@
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>196</v>
       </c>
@@ -6622,7 +6630,7 @@
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>197</v>
       </c>
@@ -6646,7 +6654,7 @@
       </c>
       <c r="J161" s="4"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>198</v>
       </c>
@@ -6666,7 +6674,7 @@
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>200</v>
       </c>
@@ -6686,7 +6694,7 @@
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>202</v>
       </c>
@@ -6706,7 +6714,7 @@
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>204</v>
       </c>
@@ -6728,7 +6736,7 @@
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>205</v>
       </c>
@@ -6758,7 +6766,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>206</v>
       </c>
@@ -6784,7 +6792,7 @@
       </c>
       <c r="J167" s="4"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>207</v>
       </c>
@@ -6810,7 +6818,7 @@
       <c r="I168" s="4"/>
       <c r="J168" s="4"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>208</v>
       </c>
@@ -6832,7 +6840,7 @@
       <c r="I169" s="4"/>
       <c r="J169" s="4"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>209</v>
       </c>
@@ -6852,7 +6860,7 @@
       <c r="I170" s="4"/>
       <c r="J170" s="4"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>211</v>
       </c>
@@ -6874,7 +6882,7 @@
       <c r="I171" s="4"/>
       <c r="J171" s="4"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>212</v>
       </c>
@@ -6900,7 +6908,7 @@
       <c r="I172" s="4"/>
       <c r="J172" s="4"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>213</v>
       </c>
@@ -6922,7 +6930,7 @@
       <c r="I173" s="4"/>
       <c r="J173" s="4"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>215</v>
       </c>
@@ -6944,7 +6952,7 @@
       <c r="I174" s="4"/>
       <c r="J174" s="4"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>216</v>
       </c>
@@ -6966,7 +6974,7 @@
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>217</v>
       </c>
@@ -6986,7 +6994,7 @@
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>219</v>
       </c>
@@ -7004,7 +7012,7 @@
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>221</v>
       </c>
@@ -7026,7 +7034,7 @@
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>222</v>
       </c>
@@ -7048,7 +7056,7 @@
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>223</v>
       </c>
@@ -7070,7 +7078,7 @@
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>224</v>
       </c>
@@ -7094,7 +7102,7 @@
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>225</v>
       </c>
@@ -7116,7 +7124,7 @@
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>227</v>
       </c>
@@ -7138,7 +7146,7 @@
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
         <v>228</v>
       </c>
@@ -7156,7 +7164,7 @@
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>230</v>
       </c>
@@ -7184,7 +7192,7 @@
       </c>
       <c r="J185" s="4"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>231</v>
       </c>
@@ -7206,7 +7214,7 @@
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>232</v>
       </c>
@@ -7232,7 +7240,7 @@
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
         <v>233</v>
       </c>
@@ -7250,12 +7258,12 @@
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C189" s="5">
         <v>3268879</v>
@@ -7272,12 +7280,12 @@
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C190" s="5">
         <v>39001020</v>
@@ -7294,12 +7302,12 @@
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>235</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C191" s="5">
         <v>35822469</v>
@@ -7316,12 +7324,12 @@
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>236</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C192" s="5">
         <v>67562394</v>
@@ -7338,12 +7346,12 @@
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>237</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C193" s="5">
         <v>55673897</v>
@@ -7360,12 +7368,12 @@
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>238</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C194" s="5">
         <v>39227286</v>
@@ -7382,12 +7390,12 @@
       <c r="I194" s="4"/>
       <c r="J194" s="4"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>239</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C195" s="5">
         <v>70648269</v>
@@ -7404,12 +7412,12 @@
       <c r="I195" s="4"/>
       <c r="J195" s="4"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>240</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C196" s="5">
         <v>57653857</v>
@@ -7426,12 +7434,12 @@
       <c r="I196" s="4"/>
       <c r="J196" s="4"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>241</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C197" s="5">
         <v>57117449</v>
@@ -7448,12 +7456,12 @@
       <c r="I197" s="4"/>
       <c r="J197" s="4"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>242</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C198" s="5">
         <v>19408743</v>
@@ -7470,12 +7478,12 @@
       <c r="I198" s="4"/>
       <c r="J198" s="4"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>243</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C199" s="5">
         <v>72918219</v>
@@ -7492,12 +7500,12 @@
       <c r="I199" s="4"/>
       <c r="J199" s="4"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>244</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C200" s="5">
         <v>40321764</v>
@@ -7514,12 +7522,12 @@
       <c r="I200" s="4"/>
       <c r="J200" s="4"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>245</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C201" s="5">
         <v>57117416</v>
@@ -7536,12 +7544,12 @@
       <c r="I201" s="4"/>
       <c r="J201" s="4"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>246</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C202" s="5">
         <v>60851345</v>
@@ -7558,12 +7566,12 @@
       <c r="I202" s="4"/>
       <c r="J202" s="4"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
         <v>247</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C203" s="5">
         <v>57117314</v>
@@ -7580,12 +7588,12 @@
       <c r="I203" s="4"/>
       <c r="J203" s="4"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>248</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C204" s="5">
         <v>1746016</v>
@@ -7602,12 +7610,12 @@
       <c r="I204" s="4"/>
       <c r="J204" s="4"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>249</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C205" s="5">
         <v>51207319</v>
@@ -7624,7 +7632,7 @@
       <c r="I205" s="4"/>
       <c r="J205" s="4"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>250</v>
       </c>
@@ -7646,7 +7654,7 @@
       <c r="I206" s="4"/>
       <c r="J206" s="4"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>252</v>
       </c>
@@ -7664,7 +7672,7 @@
       <c r="I207" s="4"/>
       <c r="J207" s="4"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>253</v>
       </c>
@@ -7696,7 +7704,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>254</v>
       </c>
@@ -7724,7 +7732,7 @@
       </c>
       <c r="J209" s="4"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>255</v>
       </c>
@@ -7750,7 +7758,7 @@
       <c r="I210" s="4"/>
       <c r="J210" s="4"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>256</v>
       </c>
@@ -7772,7 +7780,7 @@
       <c r="I211" s="4"/>
       <c r="J211" s="4"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>257</v>
       </c>
@@ -7794,7 +7802,7 @@
       <c r="I212" s="4"/>
       <c r="J212" s="4"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>258</v>
       </c>
@@ -7820,7 +7828,7 @@
       <c r="I213" s="4"/>
       <c r="J213" s="4"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>259</v>
       </c>
@@ -7846,7 +7854,7 @@
       </c>
       <c r="J214" s="4"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>260</v>
       </c>
@@ -7868,7 +7876,7 @@
       <c r="I215" s="4"/>
       <c r="J215" s="4"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>261</v>
       </c>
@@ -7892,7 +7900,7 @@
       <c r="I216" s="4"/>
       <c r="J216" s="4"/>
     </row>
-    <row r="217" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>262</v>
       </c>
@@ -7918,7 +7926,7 @@
       </c>
       <c r="J217" s="4"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>263</v>
       </c>
@@ -7938,7 +7946,7 @@
       <c r="I218" s="4"/>
       <c r="J218" s="4"/>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
         <v>264</v>
       </c>
@@ -7960,7 +7968,7 @@
       <c r="I219" s="4"/>
       <c r="J219" s="4"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>265</v>
       </c>
@@ -7992,7 +8000,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
         <v>268</v>
       </c>
@@ -8016,7 +8024,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
         <v>272</v>
       </c>
@@ -8040,7 +8048,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
         <v>271</v>
       </c>
@@ -8064,7 +8072,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
         <v>273</v>
       </c>
@@ -8086,7 +8094,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
         <v>275</v>
       </c>
@@ -8110,7 +8118,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>276</v>
       </c>
@@ -8132,7 +8140,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
         <v>279</v>
       </c>
@@ -8154,7 +8162,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
         <v>280</v>
       </c>
@@ -8178,7 +8186,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
         <v>281</v>
       </c>
@@ -8200,7 +8208,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>282</v>
       </c>
@@ -8224,7 +8232,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>283</v>
       </c>
@@ -8248,7 +8256,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
         <v>284</v>
       </c>
@@ -8272,7 +8280,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="18" t="s">
         <v>285</v>
       </c>
@@ -8294,7 +8302,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>287</v>
       </c>
@@ -8316,7 +8324,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>288</v>
       </c>
@@ -8340,7 +8348,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>289</v>
       </c>
@@ -8364,7 +8372,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>290</v>
       </c>
@@ -8388,7 +8396,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>291</v>
       </c>
@@ -8412,7 +8420,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>292</v>
       </c>
@@ -8434,7 +8442,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="18" t="s">
         <v>295</v>
       </c>
@@ -8458,7 +8466,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
         <v>296</v>
       </c>
@@ -8482,7 +8490,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
         <v>297</v>
       </c>
@@ -8504,7 +8512,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
         <v>299</v>
       </c>
@@ -8528,7 +8536,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
         <v>300</v>
       </c>
@@ -8552,7 +8560,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
         <v>301</v>
       </c>
@@ -8576,7 +8584,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
         <v>302</v>
       </c>
@@ -8598,15 +8606,15 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>267</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="4">
@@ -8620,7 +8628,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
         <v>303</v>
       </c>
@@ -8642,7 +8650,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>304</v>
       </c>
@@ -8664,7 +8672,7 @@
       <c r="I249" s="4"/>
       <c r="J249" s="4"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>305</v>
       </c>
@@ -8684,7 +8692,7 @@
       <c r="I250" s="4"/>
       <c r="J250" s="4"/>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
         <v>306</v>
       </c>
@@ -8708,7 +8716,7 @@
       </c>
       <c r="J251" s="4"/>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>307</v>
       </c>
@@ -8730,7 +8738,7 @@
       <c r="I252" s="4"/>
       <c r="J252" s="4"/>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
         <v>308</v>
       </c>
@@ -8750,7 +8758,7 @@
       <c r="I253" s="4"/>
       <c r="J253" s="4"/>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
         <v>309</v>
       </c>
@@ -8772,7 +8780,7 @@
       <c r="I254" s="4"/>
       <c r="J254" s="4"/>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
         <v>310</v>
       </c>
@@ -8790,7 +8798,7 @@
       <c r="I255" s="4"/>
       <c r="J255" s="4"/>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
         <v>311</v>
       </c>
@@ -8814,7 +8822,7 @@
       <c r="I256" s="4"/>
       <c r="J256" s="4"/>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
         <v>313</v>
       </c>
@@ -8844,7 +8852,7 @@
       </c>
       <c r="J257" s="4"/>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
         <v>314</v>
       </c>
@@ -8876,7 +8884,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
         <v>315</v>
       </c>
@@ -8908,7 +8916,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
         <v>316</v>
       </c>
@@ -8930,7 +8938,7 @@
       <c r="I260" s="4"/>
       <c r="J260" s="4"/>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
         <v>317</v>
       </c>
@@ -8950,7 +8958,7 @@
       <c r="I261" s="4"/>
       <c r="J261" s="4"/>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
         <v>318</v>
       </c>
@@ -8970,7 +8978,7 @@
       <c r="I262" s="4"/>
       <c r="J262" s="4"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
         <v>320</v>
       </c>
@@ -8990,7 +8998,7 @@
       <c r="I263" s="4"/>
       <c r="J263" s="4"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
         <v>321</v>
       </c>
@@ -9012,7 +9020,7 @@
       <c r="I264" s="4"/>
       <c r="J264" s="4"/>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
         <v>322</v>
       </c>
@@ -9034,7 +9042,7 @@
       <c r="I265" s="4"/>
       <c r="J265" s="4"/>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" s="18" t="s">
         <v>323</v>
       </c>
@@ -9056,7 +9064,7 @@
       <c r="I266" s="4"/>
       <c r="J266" s="4"/>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="18" t="s">
         <v>324</v>
       </c>
@@ -9076,7 +9084,7 @@
       <c r="I267" s="4"/>
       <c r="J267" s="4"/>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
         <v>319</v>
       </c>
@@ -9098,7 +9106,7 @@
       <c r="I268" s="4"/>
       <c r="J268" s="4"/>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
         <v>326</v>
       </c>
@@ -9118,7 +9126,7 @@
       <c r="I269" s="4"/>
       <c r="J269" s="4"/>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
         <v>327</v>
       </c>
@@ -9140,7 +9148,7 @@
       <c r="I270" s="4"/>
       <c r="J270" s="4"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
         <v>328</v>
       </c>
@@ -9160,7 +9168,7 @@
       <c r="I271" s="4"/>
       <c r="J271" s="4"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
         <v>329</v>
       </c>
@@ -9180,7 +9188,7 @@
       <c r="I272" s="4"/>
       <c r="J272" s="4"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
         <v>330</v>
       </c>
@@ -9200,7 +9208,7 @@
       <c r="I273" s="4"/>
       <c r="J273" s="4"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
         <v>331</v>
       </c>
@@ -9222,7 +9230,7 @@
       <c r="I274" s="4"/>
       <c r="J274" s="4"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
         <v>332</v>
       </c>
@@ -9244,7 +9252,7 @@
       <c r="I275" s="4"/>
       <c r="J275" s="4"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
         <v>333</v>
       </c>
@@ -9270,7 +9278,7 @@
       </c>
       <c r="J276" s="4"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
         <v>334</v>
       </c>
@@ -9290,7 +9298,7 @@
       <c r="I277" s="4"/>
       <c r="J277" s="4"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
         <v>335</v>
       </c>
@@ -9312,7 +9320,7 @@
       <c r="I278" s="4"/>
       <c r="J278" s="4"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
         <v>336</v>
       </c>
@@ -9334,7 +9342,7 @@
       <c r="I279" s="4"/>
       <c r="J279" s="4"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
         <v>337</v>
       </c>
@@ -9354,7 +9362,7 @@
       <c r="I280" s="4"/>
       <c r="J280" s="4"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
         <v>338</v>
       </c>
@@ -9374,7 +9382,7 @@
       <c r="I281" s="4"/>
       <c r="J281" s="4"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="7" t="s">
         <v>340</v>
       </c>
@@ -9396,7 +9404,7 @@
       <c r="I282" s="4"/>
       <c r="J282" s="4"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
         <v>341</v>
       </c>
@@ -9416,7 +9424,7 @@
       <c r="I283" s="4"/>
       <c r="J283" s="4"/>
     </row>
-    <row r="284" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A284" s="7" t="s">
         <v>342</v>
       </c>
@@ -9436,7 +9444,7 @@
       <c r="I284" s="4"/>
       <c r="J284" s="4"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
         <v>343</v>
       </c>
@@ -9458,7 +9466,7 @@
       <c r="I285" s="4"/>
       <c r="J285" s="4"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
         <v>344</v>
       </c>
@@ -9478,7 +9486,7 @@
       <c r="I286" s="4"/>
       <c r="J286" s="4"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
         <v>346</v>
       </c>
@@ -9498,7 +9506,7 @@
       <c r="I287" s="4"/>
       <c r="J287" s="4"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
         <v>348</v>
       </c>
@@ -9520,7 +9528,7 @@
       <c r="I288" s="4"/>
       <c r="J288" s="4"/>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
         <v>349</v>
       </c>
@@ -9540,7 +9548,7 @@
       <c r="I289" s="4"/>
       <c r="J289" s="4"/>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
         <v>351</v>
       </c>
@@ -9560,7 +9568,7 @@
       <c r="I290" s="4"/>
       <c r="J290" s="4"/>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
         <v>353</v>
       </c>
@@ -9588,7 +9596,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
         <v>354</v>
       </c>
@@ -9608,7 +9616,7 @@
       <c r="I292" s="4"/>
       <c r="J292" s="4"/>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
         <v>345</v>
       </c>
@@ -9630,7 +9638,7 @@
       <c r="I293" s="4"/>
       <c r="J293" s="4"/>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
         <v>356</v>
       </c>
@@ -9650,7 +9658,7 @@
       <c r="I294" s="4"/>
       <c r="J294" s="4"/>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
         <v>358</v>
       </c>
@@ -9672,7 +9680,7 @@
       <c r="I295" s="4"/>
       <c r="J295" s="4"/>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
         <v>359</v>
       </c>
@@ -9692,7 +9700,7 @@
       <c r="I296" s="4"/>
       <c r="J296" s="4"/>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
         <v>361</v>
       </c>
@@ -9712,7 +9720,7 @@
       <c r="I297" s="4"/>
       <c r="J297" s="4"/>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
         <v>362</v>
       </c>
@@ -9734,7 +9742,7 @@
       <c r="I298" s="4"/>
       <c r="J298" s="4"/>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
         <v>363</v>
       </c>
@@ -9766,7 +9774,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
         <v>364</v>
       </c>
@@ -9786,7 +9794,7 @@
       <c r="I300" s="4"/>
       <c r="J300" s="4"/>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
         <v>365</v>
       </c>
@@ -9814,7 +9822,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
         <v>366</v>
       </c>
@@ -9842,7 +9850,7 @@
       </c>
       <c r="J302" s="4"/>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
         <v>367</v>
       </c>
@@ -9866,7 +9874,7 @@
       <c r="I303" s="4"/>
       <c r="J303" s="4"/>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
         <v>368</v>
       </c>
@@ -9896,7 +9904,7 @@
       </c>
       <c r="J304" s="4"/>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
         <v>369</v>
       </c>
@@ -9918,7 +9926,7 @@
       <c r="I305" s="4"/>
       <c r="J305" s="4"/>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
         <v>370</v>
       </c>
@@ -9946,7 +9954,7 @@
       </c>
       <c r="J306" s="4"/>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
         <v>371</v>
       </c>
@@ -9972,7 +9980,7 @@
       <c r="I307" s="4"/>
       <c r="J307" s="4"/>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
         <v>372</v>
       </c>
@@ -10002,7 +10010,7 @@
       </c>
       <c r="J308" s="4"/>
     </row>
-    <row r="309" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>373</v>
       </c>
@@ -10034,7 +10042,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
         <v>374</v>
       </c>
@@ -10056,7 +10064,7 @@
       <c r="I310" s="4"/>
       <c r="J310" s="4"/>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
         <v>375</v>
       </c>
@@ -10078,7 +10086,7 @@
       <c r="I311" s="4"/>
       <c r="J311" s="4"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="7" t="s">
         <v>376</v>
       </c>
@@ -10100,7 +10108,7 @@
       <c r="I312" s="4"/>
       <c r="J312" s="37"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="7" t="s">
         <v>378</v>
       </c>
@@ -10122,7 +10130,7 @@
       <c r="I313" s="4"/>
       <c r="J313" s="37"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
         <v>379</v>
       </c>
@@ -10146,7 +10154,7 @@
       <c r="I314" s="4"/>
       <c r="J314" s="37"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>380</v>
       </c>
@@ -10168,7 +10176,7 @@
       <c r="I315" s="4"/>
       <c r="J315" s="37"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>377</v>
       </c>
@@ -10190,7 +10198,7 @@
       <c r="I316" s="4"/>
       <c r="J316" s="37"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
         <v>381</v>
       </c>
@@ -10212,7 +10220,7 @@
       <c r="I317" s="4"/>
       <c r="J317" s="37"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>382</v>
       </c>
@@ -10234,7 +10242,7 @@
       <c r="I318" s="4"/>
       <c r="J318" s="37"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
         <v>383</v>
       </c>
@@ -10254,7 +10262,7 @@
       <c r="I319" s="4"/>
       <c r="J319" s="37"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
         <v>385</v>
       </c>
@@ -10276,7 +10284,7 @@
       <c r="I320" s="4"/>
       <c r="J320" s="37"/>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
         <v>386</v>
       </c>
@@ -10298,7 +10306,7 @@
       <c r="I321" s="4"/>
       <c r="J321" s="37"/>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
         <v>387</v>
       </c>
@@ -10320,7 +10328,7 @@
       <c r="I322" s="4"/>
       <c r="J322" s="37"/>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
         <v>388</v>
       </c>
@@ -10342,7 +10350,7 @@
       <c r="I323" s="4"/>
       <c r="J323" s="4"/>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
         <v>389</v>
       </c>
@@ -10364,7 +10372,7 @@
       <c r="I324" s="4"/>
       <c r="J324" s="4"/>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
         <v>390</v>
       </c>
@@ -10386,7 +10394,7 @@
       <c r="I325" s="4"/>
       <c r="J325" s="4"/>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
         <v>391</v>
       </c>
@@ -10404,7 +10412,7 @@
       <c r="I326" s="4"/>
       <c r="J326" s="4"/>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
         <v>394</v>
       </c>
@@ -10426,7 +10434,7 @@
       <c r="I327" s="4"/>
       <c r="J327" s="4"/>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
         <v>395</v>
       </c>
@@ -10450,7 +10458,7 @@
       <c r="I328" s="4"/>
       <c r="J328" s="4"/>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
         <v>396</v>
       </c>
@@ -10470,7 +10478,7 @@
       <c r="I329" s="4"/>
       <c r="J329" s="4"/>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
         <v>397</v>
       </c>
@@ -10490,7 +10498,7 @@
       <c r="I330" s="4"/>
       <c r="J330" s="4"/>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
         <v>398</v>
       </c>
@@ -10522,7 +10530,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
         <v>399</v>
       </c>
@@ -10550,7 +10558,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
         <v>400</v>
       </c>
@@ -10576,7 +10584,7 @@
       </c>
       <c r="J333" s="4"/>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
         <v>401</v>
       </c>
@@ -10600,7 +10608,7 @@
       <c r="I334" s="4"/>
       <c r="J334" s="4"/>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
         <v>402</v>
       </c>
@@ -10622,7 +10630,7 @@
       <c r="I335" s="4"/>
       <c r="J335" s="4"/>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
         <v>403</v>
       </c>
@@ -10640,7 +10648,7 @@
       <c r="I336" s="4"/>
       <c r="J336" s="4"/>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
         <v>405</v>
       </c>
@@ -10662,7 +10670,7 @@
       <c r="I337" s="4"/>
       <c r="J337" s="4"/>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
         <v>407</v>
       </c>
@@ -10682,7 +10690,7 @@
       <c r="I338" s="4"/>
       <c r="J338" s="4"/>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
         <v>409</v>
       </c>
@@ -10702,7 +10710,7 @@
       <c r="I339" s="4"/>
       <c r="J339" s="4"/>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
         <v>411</v>
       </c>
@@ -10722,7 +10730,7 @@
       <c r="I340" s="4"/>
       <c r="J340" s="4"/>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
         <v>413</v>
       </c>
@@ -10744,7 +10752,7 @@
       <c r="I341" s="4"/>
       <c r="J341" s="4"/>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
         <v>414</v>
       </c>
@@ -10764,7 +10772,7 @@
       <c r="I342" s="4"/>
       <c r="J342" s="4"/>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
         <v>416</v>
       </c>
@@ -10786,15 +10794,15 @@
       <c r="I343" s="4"/>
       <c r="J343" s="4"/>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B344" s="4" t="s">
         <v>406</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D344" s="4">
         <v>1E-4</v>
@@ -10806,7 +10814,7 @@
       <c r="I344" s="4"/>
       <c r="J344" s="4"/>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
         <v>417</v>
       </c>
@@ -10826,7 +10834,7 @@
       <c r="I345" s="4"/>
       <c r="J345" s="4"/>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
         <v>418</v>
       </c>
@@ -10846,7 +10854,7 @@
       <c r="I346" s="4"/>
       <c r="J346" s="4"/>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
         <v>419</v>
       </c>
@@ -10866,7 +10874,7 @@
       <c r="I347" s="4"/>
       <c r="J347" s="4"/>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
         <v>420</v>
       </c>
@@ -10886,7 +10894,7 @@
       <c r="I348" s="4"/>
       <c r="J348" s="4"/>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
         <v>421</v>
       </c>
@@ -10906,7 +10914,7 @@
       <c r="I349" s="4"/>
       <c r="J349" s="4"/>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
         <v>422</v>
       </c>
@@ -10926,7 +10934,7 @@
       <c r="I350" s="4"/>
       <c r="J350" s="4"/>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
         <v>423</v>
       </c>
@@ -10946,7 +10954,7 @@
       <c r="I351" s="4"/>
       <c r="J351" s="4"/>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
         <v>424</v>
       </c>
@@ -10964,7 +10972,7 @@
       <c r="I352" s="4"/>
       <c r="J352" s="4"/>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
         <v>426</v>
       </c>
@@ -10984,7 +10992,7 @@
       <c r="I353" s="4"/>
       <c r="J353" s="4"/>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
         <v>428</v>
       </c>
@@ -10992,7 +11000,7 @@
         <v>429</v>
       </c>
       <c r="C354" s="38" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D354" s="31">
         <v>5.079E-5</v>
@@ -11004,7 +11012,7 @@
       <c r="I354" s="4"/>
       <c r="J354" s="4"/>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
         <v>430</v>
       </c>
@@ -11024,7 +11032,7 @@
       <c r="I355" s="4"/>
       <c r="J355" s="4"/>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
         <v>431</v>
       </c>
@@ -11042,7 +11050,7 @@
       <c r="I356" s="4"/>
       <c r="J356" s="4"/>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
         <v>433</v>
       </c>
@@ -11064,7 +11072,7 @@
       <c r="I357" s="4"/>
       <c r="J357" s="4"/>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
         <v>435</v>
       </c>
@@ -11084,15 +11092,15 @@
       <c r="I358" s="4"/>
       <c r="J358" s="4"/>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B359" s="4" t="s">
         <v>434</v>
       </c>
       <c r="C359" s="39" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D359" s="31">
         <v>5.079E-5</v>
@@ -11104,7 +11112,7 @@
       <c r="I359" s="4"/>
       <c r="J359" s="4"/>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>436</v>
       </c>
@@ -11124,7 +11132,7 @@
       <c r="I360" s="4"/>
       <c r="J360" s="4"/>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>437</v>
       </c>
@@ -11146,7 +11154,7 @@
       <c r="I361" s="4"/>
       <c r="J361" s="4"/>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362" s="7" t="s">
         <v>438</v>
       </c>
@@ -11166,7 +11174,7 @@
       <c r="I362" s="4"/>
       <c r="J362" s="4"/>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363" s="7" t="s">
         <v>440</v>
       </c>
@@ -11186,7 +11194,7 @@
       <c r="I363" s="4"/>
       <c r="J363" s="4"/>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
         <v>441</v>
       </c>
@@ -11208,7 +11216,7 @@
       <c r="I364" s="4"/>
       <c r="J364" s="4"/>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
         <v>442</v>
       </c>
@@ -11230,7 +11238,7 @@
       <c r="I365" s="4"/>
       <c r="J365" s="4"/>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
         <v>444</v>
       </c>
@@ -11252,29 +11260,31 @@
       <c r="I366" s="4"/>
       <c r="J366" s="4"/>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A367" s="4" t="s">
+    <row r="367" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A367" s="41" t="s">
         <v>445</v>
       </c>
-      <c r="B367" s="4" t="s">
+      <c r="B367" s="41" t="s">
+        <v>630</v>
+      </c>
+      <c r="C367" s="42">
+        <v>120127</v>
+      </c>
+      <c r="D367" s="43">
+        <v>5.079E-5</v>
+      </c>
+      <c r="E367" s="41">
+        <v>0</v>
+      </c>
+      <c r="F367" s="41"/>
+      <c r="G367" s="41"/>
+      <c r="H367" s="41"/>
+      <c r="I367" s="41"/>
+      <c r="J367" s="41"/>
+    </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A368" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="C367" s="5">
-        <v>120127</v>
-      </c>
-      <c r="D367" s="4"/>
-      <c r="E367" s="4">
-        <v>0</v>
-      </c>
-      <c r="F367" s="4"/>
-      <c r="G367" s="4"/>
-      <c r="H367" s="4"/>
-      <c r="I367" s="4"/>
-      <c r="J367" s="4"/>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A368" s="4" t="s">
-        <v>447</v>
       </c>
       <c r="B368" s="4" t="s">
         <v>434</v>
@@ -11292,15 +11302,15 @@
       <c r="I368" s="4"/>
       <c r="J368" s="4"/>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B369" s="4" t="s">
         <v>434</v>
       </c>
       <c r="C369" s="38" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D369" s="31">
         <v>5.079E-5</v>
@@ -11312,9 +11322,9 @@
       <c r="I369" s="4"/>
       <c r="J369" s="4"/>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B370" s="4" t="s">
         <v>434</v>
@@ -11332,9 +11342,9 @@
       <c r="I370" s="4"/>
       <c r="J370" s="4"/>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B371" s="4" t="s">
         <v>434</v>
@@ -11354,9 +11364,9 @@
       <c r="I371" s="4"/>
       <c r="J371" s="4"/>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B372" s="4" t="s">
         <v>434</v>
@@ -11374,9 +11384,9 @@
       <c r="I372" s="4"/>
       <c r="J372" s="4"/>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B373" s="4" t="s">
         <v>443</v>
@@ -11396,15 +11406,15 @@
       <c r="I373" s="4"/>
       <c r="J373" s="4"/>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B374" s="4" t="s">
         <v>432</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D374" s="31">
         <v>5.079E-5</v>
@@ -11416,9 +11426,9 @@
       <c r="I374" s="4"/>
       <c r="J374" s="4"/>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B375" s="4" t="s">
         <v>443</v>
@@ -11436,9 +11446,9 @@
       <c r="I375" s="4"/>
       <c r="J375" s="4"/>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B376" s="4" t="s">
         <v>443</v>
@@ -11458,9 +11468,9 @@
       <c r="I376" s="4"/>
       <c r="J376" s="4"/>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B377" s="4" t="s">
         <v>443</v>
@@ -11480,15 +11490,15 @@
       <c r="I377" s="4"/>
       <c r="J377" s="4"/>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B378" s="4" t="s">
         <v>434</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D378" s="31">
         <v>5.079E-5</v>
@@ -11500,9 +11510,9 @@
       <c r="I378" s="4"/>
       <c r="J378" s="4"/>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B379" s="4" t="s">
         <v>434</v>
@@ -11520,15 +11530,15 @@
       <c r="I379" s="4"/>
       <c r="J379" s="4"/>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B380" s="4" t="s">
         <v>434</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D380" s="31">
         <v>5.079E-5</v>
@@ -11540,9 +11550,9 @@
       <c r="I380" s="4"/>
       <c r="J380" s="4"/>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B381" s="4" t="s">
         <v>434</v>
@@ -11560,15 +11570,15 @@
       <c r="I381" s="4"/>
       <c r="J381" s="4"/>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B382" s="4" t="s">
         <v>434</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D382" s="31">
         <v>5.079E-5</v>
@@ -11580,9 +11590,9 @@
       <c r="I382" s="4"/>
       <c r="J382" s="4"/>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B383" s="4" t="s">
         <v>434</v>
@@ -11600,52 +11610,56 @@
       <c r="I383" s="4"/>
       <c r="J383" s="4"/>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A384" s="4" t="s">
+    <row r="384" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A384" s="41" t="s">
+        <v>464</v>
+      </c>
+      <c r="B384" s="41" t="s">
+        <v>630</v>
+      </c>
+      <c r="C384" s="42">
+        <v>85018</v>
+      </c>
+      <c r="D384" s="43">
+        <v>5.079E-5</v>
+      </c>
+      <c r="E384" s="41">
+        <v>0</v>
+      </c>
+      <c r="F384" s="41"/>
+      <c r="G384" s="41"/>
+      <c r="H384" s="41"/>
+      <c r="I384" s="41"/>
+      <c r="J384" s="41"/>
+    </row>
+    <row r="385" spans="1:10" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="41" t="s">
         <v>465</v>
       </c>
-      <c r="B384" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="C384" s="5">
-        <v>85018</v>
-      </c>
-      <c r="D384" s="4"/>
-      <c r="E384" s="4">
-        <v>0</v>
-      </c>
-      <c r="F384" s="4"/>
-      <c r="G384" s="4"/>
-      <c r="H384" s="4"/>
-      <c r="I384" s="4"/>
-      <c r="J384" s="4"/>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A385" s="4" t="s">
+      <c r="B385" s="41" t="s">
+        <v>630</v>
+      </c>
+      <c r="C385" s="42">
+        <v>129000</v>
+      </c>
+      <c r="D385" s="43">
+        <v>5.079E-5</v>
+      </c>
+      <c r="E385" s="41">
+        <v>0</v>
+      </c>
+      <c r="F385" s="41"/>
+      <c r="G385" s="41"/>
+      <c r="H385" s="41"/>
+      <c r="I385" s="41"/>
+      <c r="J385" s="41"/>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A386" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="B385" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="C385" s="5">
-        <v>129000</v>
-      </c>
-      <c r="D385" s="4"/>
-      <c r="E385" s="4">
-        <v>0</v>
-      </c>
-      <c r="F385" s="4"/>
-      <c r="G385" s="4"/>
-      <c r="H385" s="4"/>
-      <c r="I385" s="4"/>
-      <c r="J385" s="4"/>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A386" s="4" t="s">
+      <c r="B386" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="B386" s="4" t="s">
-        <v>468</v>
       </c>
       <c r="C386" s="5"/>
       <c r="D386" s="31">
@@ -11658,12 +11672,12 @@
       <c r="I386" s="4"/>
       <c r="J386" s="4"/>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B387" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="B387" s="4" t="s">
-        <v>470</v>
       </c>
       <c r="C387" s="5">
         <v>57976</v>
@@ -11680,12 +11694,12 @@
       <c r="I387" s="4"/>
       <c r="J387" s="4"/>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B388" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="B388" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="C388" s="5"/>
       <c r="D388" s="31">
@@ -11698,12 +11712,12 @@
       <c r="I388" s="4"/>
       <c r="J388" s="4"/>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B389" s="4" t="s">
         <v>473</v>
-      </c>
-      <c r="B389" s="4" t="s">
-        <v>474</v>
       </c>
       <c r="C389" s="5">
         <v>42397648</v>
@@ -11720,12 +11734,12 @@
       <c r="I389" s="4"/>
       <c r="J389" s="4"/>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C390" s="5">
         <v>56495</v>
@@ -11742,12 +11756,12 @@
       <c r="I390" s="4"/>
       <c r="J390" s="4"/>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C391" s="5">
         <v>7496028</v>
@@ -11764,12 +11778,12 @@
       <c r="I391" s="4"/>
       <c r="J391" s="4"/>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C392" s="5">
         <v>189640</v>
@@ -11786,12 +11800,12 @@
       <c r="I392" s="4"/>
       <c r="J392" s="4"/>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C393" s="5">
         <v>189559</v>
@@ -11808,12 +11822,12 @@
       <c r="I393" s="4"/>
       <c r="J393" s="4"/>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C394" s="5">
         <v>191300</v>
@@ -11830,12 +11844,12 @@
       <c r="I394" s="4"/>
       <c r="J394" s="4"/>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B395" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="B395" s="4" t="s">
-        <v>481</v>
       </c>
       <c r="C395" s="5"/>
       <c r="D395" s="31">
@@ -11848,12 +11862,12 @@
       <c r="I395" s="4"/>
       <c r="J395" s="4"/>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B396" s="4" t="s">
         <v>482</v>
-      </c>
-      <c r="B396" s="4" t="s">
-        <v>483</v>
       </c>
       <c r="C396" s="5">
         <v>42397659</v>
@@ -11870,15 +11884,15 @@
       <c r="I396" s="4"/>
       <c r="J396" s="4"/>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C397" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="B397" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="C397" s="5" t="s">
-        <v>485</v>
       </c>
       <c r="D397" s="4">
         <v>2.1540000000000001E-3</v>
@@ -11890,15 +11904,15 @@
       <c r="I397" s="4"/>
       <c r="J397" s="4"/>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B398" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="B398" s="4" t="s">
+      <c r="C398" s="5" t="s">
         <v>615</v>
-      </c>
-      <c r="C398" s="5" t="s">
-        <v>616</v>
       </c>
       <c r="D398" s="31">
         <v>1.016E-3</v>
@@ -11910,12 +11924,12 @@
       <c r="I398" s="4"/>
       <c r="J398" s="4"/>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C399" s="5">
         <v>3697243</v>
@@ -11932,12 +11946,12 @@
       <c r="I399" s="4"/>
       <c r="J399" s="4"/>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C400" s="5">
         <v>194592</v>
@@ -11954,12 +11968,12 @@
       <c r="I400" s="4"/>
       <c r="J400" s="4"/>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B401" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="B401" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="C401" s="5">
         <v>50328</v>
@@ -11976,12 +11990,12 @@
       <c r="I401" s="4"/>
       <c r="J401" s="4"/>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C402" s="5">
         <v>192654</v>
@@ -11998,12 +12012,12 @@
       <c r="I402" s="4"/>
       <c r="J402" s="4"/>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C403" s="5">
         <v>53703</v>
@@ -12020,15 +12034,15 @@
       <c r="I403" s="4"/>
       <c r="J403" s="4"/>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C404" s="5" t="s">
         <v>492</v>
-      </c>
-      <c r="B404" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="C404" s="5" t="s">
-        <v>493</v>
       </c>
       <c r="D404" s="31">
         <v>1.016E-3</v>
@@ -12042,12 +12056,12 @@
       <c r="I404" s="4"/>
       <c r="J404" s="4"/>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B405" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="B405" s="4" t="s">
-        <v>495</v>
       </c>
       <c r="C405" s="5"/>
       <c r="D405" s="31">
@@ -12060,12 +12074,12 @@
       <c r="I405" s="4"/>
       <c r="J405" s="4"/>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B406" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="B406" s="4" t="s">
-        <v>497</v>
       </c>
       <c r="C406" s="5">
         <v>5522430</v>
@@ -12082,12 +12096,12 @@
       <c r="I406" s="4"/>
       <c r="J406" s="4"/>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C407" s="5">
         <v>57835924</v>
@@ -12104,12 +12118,12 @@
       <c r="I407" s="4"/>
       <c r="J407" s="4"/>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C408" s="5">
         <v>602879</v>
@@ -12126,12 +12140,12 @@
       <c r="I408" s="4"/>
       <c r="J408" s="4"/>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B409" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="B409" s="4" t="s">
-        <v>501</v>
       </c>
       <c r="C409" s="5">
         <v>56553</v>
@@ -12148,12 +12162,12 @@
       <c r="I409" s="4"/>
       <c r="J409" s="4"/>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C410" s="5">
         <v>205992</v>
@@ -12170,12 +12184,12 @@
       <c r="I410" s="4"/>
       <c r="J410" s="4"/>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A411" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C411" s="38">
         <v>102</v>
@@ -12190,12 +12204,12 @@
       <c r="I411" s="4"/>
       <c r="J411" s="4"/>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C412" s="5">
         <v>205823</v>
@@ -12212,12 +12226,12 @@
       <c r="I412" s="4"/>
       <c r="J412" s="4"/>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C413" s="5">
         <v>226368</v>
@@ -12234,12 +12248,12 @@
       <c r="I413" s="4"/>
       <c r="J413" s="4"/>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C414" s="5">
         <v>224420</v>
@@ -12256,12 +12270,12 @@
       <c r="I414" s="4"/>
       <c r="J414" s="4"/>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C415" s="5">
         <v>193395</v>
@@ -12278,12 +12292,12 @@
       <c r="I415" s="4"/>
       <c r="J415" s="4"/>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B416" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="B416" s="4" t="s">
-        <v>512</v>
       </c>
       <c r="C416" s="5"/>
       <c r="D416" s="31">
@@ -12296,12 +12310,12 @@
       <c r="I416" s="4"/>
       <c r="J416" s="4"/>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C417" s="5">
         <v>207089</v>
@@ -12318,15 +12332,15 @@
       <c r="I417" s="4"/>
       <c r="J417" s="4"/>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B418" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="B418" s="4" t="s">
+      <c r="C418" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="C418" s="5" t="s">
-        <v>515</v>
       </c>
       <c r="D418" s="34">
         <v>1.558E-5</v>
@@ -12338,12 +12352,12 @@
       <c r="I418" s="4"/>
       <c r="J418" s="4"/>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C419" s="5">
         <v>607578</v>
@@ -12360,12 +12374,12 @@
       <c r="I419" s="4"/>
       <c r="J419" s="4"/>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C420" s="5">
         <v>86748</v>
@@ -12382,18 +12396,18 @@
       <c r="I420" s="4"/>
       <c r="J420" s="4"/>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C421" s="5">
         <v>218019</v>
       </c>
       <c r="D421" s="40" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E421" s="4">
         <v>0</v>
@@ -12404,12 +12418,12 @@
       <c r="I421" s="4"/>
       <c r="J421" s="4"/>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B422" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="B422" s="4" t="s">
-        <v>521</v>
       </c>
       <c r="C422" s="5"/>
       <c r="D422" s="31">
@@ -12422,12 +12436,12 @@
       <c r="I422" s="4"/>
       <c r="J422" s="4"/>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B423" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="B423" s="4" t="s">
-        <v>523</v>
       </c>
       <c r="C423" s="14">
         <v>75</v>
@@ -12442,12 +12456,12 @@
       <c r="I423" s="4"/>
       <c r="J423" s="4"/>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C424" s="5">
         <v>106503</v>
@@ -12464,12 +12478,12 @@
       <c r="I424" s="4"/>
       <c r="J424" s="4"/>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C425" s="5">
         <v>123386</v>
@@ -12490,12 +12504,12 @@
       <c r="I425" s="4"/>
       <c r="J425" s="4"/>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C426" s="5">
         <v>114261</v>
@@ -12512,12 +12526,12 @@
       <c r="I426" s="4"/>
       <c r="J426" s="4"/>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C427" s="5">
         <v>78875</v>
@@ -12532,12 +12546,12 @@
       <c r="I427" s="4"/>
       <c r="J427" s="4"/>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C428" s="5">
         <v>75569</v>
@@ -12564,12 +12578,12 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C429" s="5">
         <v>91225</v>
@@ -12586,12 +12600,12 @@
       <c r="I429" s="4"/>
       <c r="J429" s="4"/>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C430" s="5">
         <v>106514</v>
@@ -12608,12 +12622,12 @@
       <c r="I430" s="4"/>
       <c r="J430" s="4"/>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C431" s="38">
         <v>605</v>
@@ -12626,15 +12640,15 @@
       <c r="I431" s="4"/>
       <c r="J431" s="4"/>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C432" s="39" t="s">
         <v>532</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C432" s="39" t="s">
-        <v>533</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -12644,15 +12658,15 @@
       <c r="I432" s="4"/>
       <c r="J432" s="4"/>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C433" s="38" t="s">
         <v>534</v>
-      </c>
-      <c r="B433" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C433" s="38" t="s">
-        <v>535</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -12662,12 +12676,12 @@
       <c r="I433" s="4"/>
       <c r="J433" s="4"/>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C434" s="38"/>
       <c r="D434" s="4"/>
@@ -12678,12 +12692,12 @@
       <c r="I434" s="4"/>
       <c r="J434" s="4"/>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C435" s="38"/>
       <c r="D435" s="4"/>
@@ -12694,12 +12708,12 @@
       <c r="I435" s="4"/>
       <c r="J435" s="4"/>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C436" s="8">
         <v>7440611</v>
@@ -12714,15 +12728,15 @@
       <c r="I436" s="4"/>
       <c r="J436" s="4"/>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C437" s="5" t="s">
         <v>539</v>
-      </c>
-      <c r="B437" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C437" s="5" t="s">
-        <v>540</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4">
@@ -12736,12 +12750,12 @@
       </c>
       <c r="J437" s="4"/>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C438" s="5">
         <v>7440611</v>
@@ -12758,12 +12772,12 @@
       <c r="I438" s="4"/>
       <c r="J438" s="4"/>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C439" s="5">
         <v>7783815</v>
@@ -12788,15 +12802,15 @@
       </c>
       <c r="J439" s="4"/>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C440" s="5" t="s">
         <v>543</v>
-      </c>
-      <c r="B440" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C440" s="5" t="s">
-        <v>544</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4">
@@ -12810,15 +12824,15 @@
       </c>
       <c r="J440" s="4"/>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A441" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C441" s="5" t="s">
         <v>545</v>
-      </c>
-      <c r="B441" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C441" s="5" t="s">
-        <v>546</v>
       </c>
       <c r="D441" s="4">
         <v>0</v>
@@ -12832,15 +12846,15 @@
       <c r="I441" s="4"/>
       <c r="J441" s="4"/>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B442" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C442" s="5" t="s">
         <v>547</v>
-      </c>
-      <c r="B442" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C442" s="5" t="s">
-        <v>548</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4">
@@ -12852,15 +12866,15 @@
       <c r="I442" s="4"/>
       <c r="J442" s="4"/>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C443" s="5" t="s">
         <v>549</v>
-      </c>
-      <c r="B443" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="C443" s="5" t="s">
-        <v>550</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4">
@@ -12872,12 +12886,12 @@
       <c r="I443" s="4"/>
       <c r="J443" s="4"/>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="B444" s="4" t="s">
         <v>551</v>
-      </c>
-      <c r="B444" s="4" t="s">
-        <v>552</v>
       </c>
       <c r="C444" s="5">
         <v>7783075</v>
@@ -12898,15 +12912,15 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C445" s="5" t="s">
         <v>553</v>
-      </c>
-      <c r="B445" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C445" s="5" t="s">
-        <v>554</v>
       </c>
       <c r="D445" s="35"/>
       <c r="E445" s="4">
@@ -12918,12 +12932,12 @@
       <c r="I445" s="4"/>
       <c r="J445" s="4"/>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C446" s="5">
         <v>7783008</v>
@@ -12940,12 +12954,12 @@
       <c r="I446" s="4"/>
       <c r="J446" s="4"/>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A447" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C447" s="5">
         <v>7782492</v>
@@ -12962,12 +12976,12 @@
       <c r="I447" s="4"/>
       <c r="J447" s="4"/>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C448" s="5">
         <v>7446084</v>
@@ -12982,15 +12996,15 @@
       <c r="I448" s="4"/>
       <c r="J448" s="4"/>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C449" s="5" t="s">
         <v>557</v>
-      </c>
-      <c r="B449" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C449" s="5" t="s">
-        <v>558</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4">
@@ -13002,12 +13016,12 @@
       <c r="I449" s="4"/>
       <c r="J449" s="4"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C450" s="5">
         <v>7783791</v>
@@ -13026,12 +13040,12 @@
       <c r="I450" s="4"/>
       <c r="J450" s="4"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C451" s="5">
         <v>12640890</v>
@@ -13046,15 +13060,15 @@
       <c r="I451" s="4"/>
       <c r="J451" s="4"/>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C452" s="5" t="s">
         <v>561</v>
-      </c>
-      <c r="B452" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C452" s="5" t="s">
-        <v>562</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4">
@@ -13066,15 +13080,15 @@
       <c r="I452" s="4"/>
       <c r="J452" s="4"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B453" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C453" s="5" t="s">
         <v>563</v>
-      </c>
-      <c r="B453" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C453" s="5" t="s">
-        <v>564</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4">
@@ -13086,12 +13100,12 @@
       <c r="I453" s="4"/>
       <c r="J453" s="4"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A454" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C454" s="5">
         <v>630104</v>
@@ -13108,15 +13122,15 @@
       <c r="I454" s="4"/>
       <c r="J454" s="4"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A455" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C455" s="12" t="s">
         <v>566</v>
-      </c>
-      <c r="B455" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C455" s="12" t="s">
-        <v>567</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4">
@@ -13128,15 +13142,15 @@
       <c r="I455" s="4"/>
       <c r="J455" s="4"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A456" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C456" s="12" t="s">
         <v>568</v>
-      </c>
-      <c r="B456" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="C456" s="12" t="s">
-        <v>569</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4">
@@ -13148,12 +13162,12 @@
       <c r="I456" s="4"/>
       <c r="J456" s="4"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A457" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C457" s="5">
         <v>100425</v>
@@ -13180,12 +13194,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A458" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C458" s="5">
         <v>96093</v>
@@ -13200,12 +13214,12 @@
       <c r="I458" s="4"/>
       <c r="J458" s="4"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A459" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C459" s="5">
         <v>127184</v>
@@ -13232,12 +13246,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C460" s="5">
         <v>7550450</v>
@@ -13260,12 +13274,12 @@
       </c>
       <c r="J460" s="4"/>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C461" s="5">
         <v>108883</v>
@@ -13290,12 +13304,12 @@
       </c>
       <c r="J461" s="4"/>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A462" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C462" s="5">
         <v>8001352</v>
@@ -13312,12 +13326,12 @@
       <c r="I462" s="4"/>
       <c r="J462" s="4"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A463" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C463" s="5">
         <v>79016</v>
@@ -13342,12 +13356,12 @@
       </c>
       <c r="J463" s="4"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A464" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C464" s="5">
         <v>121448</v>
@@ -13366,12 +13380,12 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C465" s="5">
         <v>1582098</v>
@@ -13386,12 +13400,12 @@
       <c r="I465" s="4"/>
       <c r="J465" s="4"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C466" s="5">
         <v>108054</v>
@@ -13400,7 +13414,7 @@
         <v>0</v>
       </c>
       <c r="E466" s="4">
-        <v>0.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F466" s="4">
         <v>24</v>
@@ -13416,12 +13430,12 @@
       </c>
       <c r="J466" s="4"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A467" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C467" s="5">
         <v>593602</v>
@@ -13438,12 +13452,12 @@
       <c r="I467" s="4"/>
       <c r="J467" s="4"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C468" s="5">
         <v>75014</v>
@@ -13470,12 +13484,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A469" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C469" s="5">
         <v>75354</v>
@@ -13494,12 +13508,12 @@
       </c>
       <c r="J469" s="4"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A470" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B470" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="B470" s="4" t="s">
-        <v>584</v>
       </c>
       <c r="C470" s="5">
         <v>108383</v>
@@ -13518,12 +13532,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A471" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C471" s="5">
         <v>95476</v>
@@ -13542,12 +13556,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A472" s="21" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B472" s="21" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C472" s="20">
         <v>106423</v>
@@ -13566,12 +13580,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A473" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C473" s="5">
         <v>1330207</v>
@@ -13594,15 +13608,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A474" s="22" t="s">
+        <v>587</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C474" s="5" t="s">
         <v>588</v>
-      </c>
-      <c r="B474" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="C474" s="5" t="s">
-        <v>589</v>
       </c>
       <c r="D474" s="4"/>
       <c r="E474" s="4"/>
@@ -13612,7 +13626,7 @@
       <c r="I474" s="24"/>
       <c r="J474" s="23"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A475" s="18" t="s">
         <v>266</v>
       </c>
@@ -13632,7 +13646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A476" s="7" t="s">
         <v>269</v>
       </c>
@@ -13650,7 +13664,7 @@
       <c r="I476" s="4"/>
       <c r="J476" s="4"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
         <v>274</v>
       </c>
@@ -13668,7 +13682,7 @@
       <c r="I477" s="4"/>
       <c r="J477" s="4"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
         <v>277</v>
       </c>
@@ -13686,7 +13700,7 @@
       <c r="I478" s="4"/>
       <c r="J478" s="4"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A479" s="7" t="s">
         <v>278</v>
       </c>
@@ -13704,15 +13718,15 @@
       <c r="I479" s="4"/>
       <c r="J479" s="4"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A480" s="18" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B480" s="4" t="s">
         <v>267</v>
       </c>
       <c r="C480" s="19" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D480" s="4"/>
       <c r="E480" s="4"/>
@@ -13722,7 +13736,7 @@
       <c r="I480" s="4"/>
       <c r="J480" s="4"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
         <v>293</v>
       </c>
@@ -13740,9 +13754,9 @@
       <c r="I481" s="4"/>
       <c r="J481" s="4"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B482" s="4"/>
       <c r="C482" s="5"/>
@@ -13754,9 +13768,9 @@
       <c r="I482" s="25"/>
       <c r="J482" s="25"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A483" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B483" s="4"/>
       <c r="C483" s="5"/>
@@ -13768,9 +13782,9 @@
       <c r="I483" s="25"/>
       <c r="J483" s="25"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A484" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B484" s="4"/>
       <c r="C484" s="5"/>
@@ -13782,9 +13796,9 @@
       <c r="I484" s="25"/>
       <c r="J484" s="25"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A485" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B485" s="4"/>
       <c r="C485" s="5"/>
@@ -13796,9 +13810,9 @@
       <c r="I485" s="25"/>
       <c r="J485" s="25"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B486" s="4"/>
       <c r="C486" s="5"/>
@@ -13810,9 +13824,9 @@
       <c r="I486" s="25"/>
       <c r="J486" s="25"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B487" s="4"/>
       <c r="C487" s="5"/>
@@ -13824,9 +13838,9 @@
       <c r="I487" s="25"/>
       <c r="J487" s="25"/>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B488" s="4"/>
       <c r="C488" s="5"/>
@@ -13838,9 +13852,9 @@
       <c r="I488" s="25"/>
       <c r="J488" s="25"/>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B489" s="4"/>
       <c r="C489" s="5"/>
@@ -13852,9 +13866,9 @@
       <c r="I489" s="25"/>
       <c r="J489" s="25"/>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A490" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B490" s="4"/>
       <c r="C490" s="5"/>
@@ -13866,9 +13880,9 @@
       <c r="I490" s="25"/>
       <c r="J490" s="25"/>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A491" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B491" s="4"/>
       <c r="C491" s="5"/>
@@ -13880,9 +13894,9 @@
       <c r="I491" s="25"/>
       <c r="J491" s="25"/>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B492" s="4"/>
       <c r="C492" s="5"/>
@@ -13894,9 +13908,9 @@
       <c r="I492" s="25"/>
       <c r="J492" s="25"/>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B493" s="4"/>
       <c r="C493" s="5"/>
@@ -13908,9 +13922,9 @@
       <c r="I493" s="25"/>
       <c r="J493" s="25"/>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A494" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B494" s="4"/>
       <c r="C494" s="5"/>
@@ -13922,9 +13936,9 @@
       <c r="I494" s="25"/>
       <c r="J494" s="25"/>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A495" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B495" s="4"/>
       <c r="C495" s="5"/>
@@ -13936,9 +13950,9 @@
       <c r="I495" s="25"/>
       <c r="J495" s="25"/>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A496" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B496" s="4"/>
       <c r="C496" s="5"/>
@@ -13950,9 +13964,9 @@
       <c r="I496" s="25"/>
       <c r="J496" s="25"/>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B497" s="4"/>
       <c r="C497" s="5"/>
@@ -13964,9 +13978,9 @@
       <c r="I497" s="25"/>
       <c r="J497" s="25"/>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A498" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B498" s="4"/>
       <c r="D498" s="4"/>
@@ -13977,9 +13991,9 @@
       <c r="I498" s="25"/>
       <c r="J498" s="25"/>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A499" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B499" s="4"/>
       <c r="C499" s="5"/>
@@ -13997,7 +14011,7 @@
   <pageMargins left="0.17" right="0.17" top="0.47" bottom="0.57999999999999996" header="0" footer="0"/>
   <pageSetup paperSize="5" scale="89" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;F&amp;C&amp;P&amp;RMay 6, 2025</oddFooter>
+    <oddFooter>&amp;L&amp;F&amp;C&amp;P&amp;ROctober, 2025</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
